--- a/nr-update-smart-card/ig/StructureDefinition-as-dr-practitioner.xlsx
+++ b/nr-update-smart-card/ig/StructureDefinition-as-dr-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15055" uniqueCount="1063">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15055" uniqueCount="1062">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T12:44:27+00:00</t>
+    <t>2025-03-18T12:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1277,9 +1277,6 @@
   </si>
   <si>
     <t>oppositionDate</t>
-  </si>
-  <si>
-    <t>CarteProfessionnel.dateOpposition</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-smartcard.extension:oppositionDate.id</t>
@@ -18571,7 +18568,7 @@
         <v>102</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>84</v>
@@ -18670,7 +18667,7 @@
         <v>84</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>408</v>
+        <v>84</v>
       </c>
       <c r="AR112" t="s" s="2">
         <v>84</v>
@@ -18687,7 +18684,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>238</v>
@@ -18820,7 +18817,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>240</v>
@@ -18953,7 +18950,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>242</v>
@@ -19088,7 +19085,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>248</v>
@@ -19221,7 +19218,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>319</v>
@@ -19264,7 +19261,7 @@
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>84</v>
@@ -19356,7 +19353,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>322</v>
@@ -19489,13 +19486,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>215</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>84</v>
@@ -19517,13 +19514,13 @@
         <v>84</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -19624,7 +19621,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>231</v>
@@ -19757,7 +19754,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>233</v>
@@ -19892,13 +19889,13 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>233</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>84</v>
@@ -19923,7 +19920,7 @@
         <v>123</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="M122" t="s" s="2">
         <v>217</v>
@@ -20027,7 +20024,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>238</v>
@@ -20160,7 +20157,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>240</v>
@@ -20293,7 +20290,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>242</v>
@@ -20336,7 +20333,7 @@
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>84</v>
@@ -20428,7 +20425,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>248</v>
@@ -20561,13 +20558,13 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>233</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>84</v>
@@ -20592,7 +20589,7 @@
         <v>123</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="M127" t="s" s="2">
         <v>217</v>
@@ -20696,7 +20693,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>238</v>
@@ -20829,7 +20826,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>240</v>
@@ -20962,7 +20959,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>242</v>
@@ -21005,7 +21002,7 @@
       </c>
       <c r="Q130" s="2"/>
       <c r="R130" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="S130" t="s" s="2">
         <v>84</v>
@@ -21097,7 +21094,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>248</v>
@@ -21230,13 +21227,13 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>233</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>84</v>
@@ -21261,7 +21258,7 @@
         <v>123</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="M132" t="s" s="2">
         <v>217</v>
@@ -21365,7 +21362,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>238</v>
@@ -21498,7 +21495,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>240</v>
@@ -21631,7 +21628,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>242</v>
@@ -21674,7 +21671,7 @@
       </c>
       <c r="Q135" s="2"/>
       <c r="R135" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="S135" t="s" s="2">
         <v>84</v>
@@ -21766,7 +21763,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>248</v>
@@ -21899,13 +21896,13 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>233</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>84</v>
@@ -21930,7 +21927,7 @@
         <v>123</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="M137" t="s" s="2">
         <v>217</v>
@@ -22034,7 +22031,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>238</v>
@@ -22167,7 +22164,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>240</v>
@@ -22300,7 +22297,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>242</v>
@@ -22343,7 +22340,7 @@
       </c>
       <c r="Q140" s="2"/>
       <c r="R140" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="S140" t="s" s="2">
         <v>84</v>
@@ -22435,7 +22432,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>248</v>
@@ -22568,7 +22565,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>271</v>
@@ -22701,7 +22698,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>273</v>
@@ -22836,7 +22833,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>275</v>
@@ -22865,7 +22862,7 @@
         <v>276</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="M144" t="s" s="2">
         <v>278</v>
@@ -22971,7 +22968,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>286</v>
@@ -23000,7 +22997,7 @@
         <v>276</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="M145" t="s" s="2">
         <v>288</v>
@@ -23108,13 +23105,13 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>233</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D146" t="s" s="2">
         <v>84</v>
@@ -23243,7 +23240,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>238</v>
@@ -23376,7 +23373,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>240</v>
@@ -23509,7 +23506,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>242</v>
@@ -23552,7 +23549,7 @@
       </c>
       <c r="Q149" s="2"/>
       <c r="R149" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S149" t="s" s="2">
         <v>84</v>
@@ -23644,7 +23641,7 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>248</v>
@@ -23777,13 +23774,13 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>233</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D151" t="s" s="2">
         <v>84</v>
@@ -23808,7 +23805,7 @@
         <v>123</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="M151" t="s" s="2">
         <v>217</v>
@@ -23912,7 +23909,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>238</v>
@@ -24045,7 +24042,7 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>240</v>
@@ -24178,7 +24175,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>242</v>
@@ -24221,7 +24218,7 @@
       </c>
       <c r="Q154" s="2"/>
       <c r="R154" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="S154" t="s" s="2">
         <v>84</v>
@@ -24313,7 +24310,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>248</v>
@@ -24446,13 +24443,13 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>233</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D156" t="s" s="2">
         <v>84</v>
@@ -24477,7 +24474,7 @@
         <v>123</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="M156" t="s" s="2">
         <v>217</v>
@@ -24581,7 +24578,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>238</v>
@@ -24714,7 +24711,7 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>240</v>
@@ -24847,7 +24844,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>242</v>
@@ -24890,7 +24887,7 @@
       </c>
       <c r="Q159" s="2"/>
       <c r="R159" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="S159" t="s" s="2">
         <v>84</v>
@@ -24982,7 +24979,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>248</v>
@@ -25008,7 +25005,7 @@
         <v>84</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L160" t="s" s="2">
         <v>250</v>
@@ -25115,7 +25112,7 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>319</v>
@@ -25158,7 +25155,7 @@
       </c>
       <c r="Q161" s="2"/>
       <c r="R161" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="S161" t="s" s="2">
         <v>84</v>
@@ -25250,7 +25247,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>322</v>
@@ -25383,10 +25380,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -25412,16 +25409,16 @@
         <v>123</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="N163" t="s" s="2">
         <v>126</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>84</v>
@@ -25470,7 +25467,7 @@
         <v>84</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>85</v>
@@ -25520,10 +25517,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -25546,17 +25543,17 @@
         <v>103</v>
       </c>
       <c r="K164" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L164" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="L164" t="s" s="2">
+      <c r="M164" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>84</v>
@@ -25593,10 +25590,10 @@
         <v>84</v>
       </c>
       <c r="AB164" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AC164" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AC164" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AD164" t="s" s="2">
         <v>84</v>
@@ -25605,7 +25602,7 @@
         <v>129</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>85</v>
@@ -25641,27 +25638,27 @@
         <v>84</v>
       </c>
       <c r="AR164" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AS164" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AS164" t="s" s="2">
+      <c r="AT164" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="AT164" t="s" s="2">
+      <c r="AU164" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="AU164" t="s" s="2">
-        <v>496</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C165" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="C165" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="D165" t="s" s="2">
         <v>84</v>
@@ -25683,17 +25680,17 @@
         <v>103</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>84</v>
@@ -25742,7 +25739,7 @@
         <v>84</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>85</v>
@@ -25769,7 +25766,7 @@
         <v>84</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AP165" t="s" s="2">
         <v>84</v>
@@ -25778,24 +25775,24 @@
         <v>84</v>
       </c>
       <c r="AR165" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AS165" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AS165" t="s" s="2">
+      <c r="AT165" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="AT165" t="s" s="2">
+      <c r="AU165" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="AU165" t="s" s="2">
-        <v>496</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B166" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="B166" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -25925,10 +25922,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B167" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -26060,10 +26057,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B168" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -26089,16 +26086,16 @@
         <v>191</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M168" t="s" s="2">
+      <c r="N168" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N168" t="s" s="2">
+      <c r="O168" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>84</v>
@@ -26126,28 +26123,28 @@
         <v>252</v>
       </c>
       <c r="Y168" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="Z168" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="Z168" t="s" s="2">
+      <c r="AA168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF168" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AA168" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB168" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC168" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD168" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE168" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF168" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>85</v>
@@ -26186,7 +26183,7 @@
         <v>214</v>
       </c>
       <c r="AS168" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AT168" t="s" s="2">
         <v>84</v>
@@ -26197,10 +26194,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B169" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="B169" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -26226,16 +26223,16 @@
         <v>249</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M169" t="s" s="2">
+      <c r="N169" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="N169" t="s" s="2">
+      <c r="O169" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>84</v>
@@ -26245,7 +26242,7 @@
         <v>84</v>
       </c>
       <c r="S169" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="T169" t="s" s="2">
         <v>84</v>
@@ -26263,28 +26260,28 @@
         <v>173</v>
       </c>
       <c r="Y169" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="Z169" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="Z169" t="s" s="2">
+      <c r="AA169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF169" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="AA169" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB169" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC169" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD169" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE169" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF169" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>85</v>
@@ -26320,10 +26317,10 @@
         <v>84</v>
       </c>
       <c r="AR169" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AS169" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AT169" t="s" s="2">
         <v>84</v>
@@ -26334,10 +26331,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B170" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="B170" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -26363,16 +26360,16 @@
         <v>149</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="M170" t="s" s="2">
+      <c r="N170" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="N170" t="s" s="2">
+      <c r="O170" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>84</v>
@@ -26382,46 +26379,46 @@
         <v>84</v>
       </c>
       <c r="S170" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="T170" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="T170" t="s" s="2">
+      <c r="U170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF170" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="U170" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V170" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W170" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X170" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y170" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z170" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA170" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB170" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC170" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD170" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE170" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF170" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>85</v>
@@ -26457,13 +26454,13 @@
         <v>84</v>
       </c>
       <c r="AR170" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AS170" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AS170" t="s" s="2">
+      <c r="AT170" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AT170" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="AU170" t="s" s="2">
         <v>84</v>
@@ -26471,10 +26468,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B171" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="B171" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -26500,13 +26497,13 @@
         <v>116</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M171" t="s" s="2">
+      <c r="N171" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -26520,43 +26517,43 @@
         <v>84</v>
       </c>
       <c r="T171" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="U171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF171" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="U171" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V171" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W171" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X171" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y171" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z171" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA171" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB171" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC171" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD171" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE171" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF171" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>85</v>
@@ -26592,13 +26589,13 @@
         <v>84</v>
       </c>
       <c r="AR171" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AS171" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="AS171" t="s" s="2">
+      <c r="AT171" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AT171" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="AU171" t="s" s="2">
         <v>84</v>
@@ -26606,10 +26603,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B172" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="B172" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -26635,10 +26632,10 @@
         <v>269</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -26689,7 +26686,7 @@
         <v>84</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>85</v>
@@ -26725,13 +26722,13 @@
         <v>84</v>
       </c>
       <c r="AR172" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AS172" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="AS172" t="s" s="2">
+      <c r="AT172" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="AT172" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="AU172" t="s" s="2">
         <v>84</v>
@@ -26739,10 +26736,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B173" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="B173" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -26765,16 +26762,16 @@
         <v>103</v>
       </c>
       <c r="K173" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L173" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L173" t="s" s="2">
+      <c r="M173" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M173" t="s" s="2">
+      <c r="N173" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -26824,7 +26821,7 @@
         <v>84</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>85</v>
@@ -26860,13 +26857,13 @@
         <v>84</v>
       </c>
       <c r="AR173" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AS173" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AS173" t="s" s="2">
+      <c r="AT173" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="AT173" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="AU173" t="s" s="2">
         <v>84</v>
@@ -26874,13 +26871,13 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C174" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="C174" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="D174" t="s" s="2">
         <v>84</v>
@@ -26902,17 +26899,17 @@
         <v>103</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>84</v>
@@ -26961,7 +26958,7 @@
         <v>84</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>85</v>
@@ -26988,7 +26985,7 @@
         <v>84</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AP174" t="s" s="2">
         <v>84</v>
@@ -26997,24 +26994,24 @@
         <v>84</v>
       </c>
       <c r="AR174" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AS174" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AS174" t="s" s="2">
+      <c r="AT174" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="AT174" t="s" s="2">
+      <c r="AU174" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="AU174" t="s" s="2">
-        <v>496</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -27144,10 +27141,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -27279,10 +27276,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -27308,16 +27305,16 @@
         <v>191</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M177" t="s" s="2">
+      <c r="N177" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N177" t="s" s="2">
+      <c r="O177" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>84</v>
@@ -27345,28 +27342,28 @@
         <v>252</v>
       </c>
       <c r="Y177" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="Z177" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="Z177" t="s" s="2">
+      <c r="AA177" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB177" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC177" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD177" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE177" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF177" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AA177" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB177" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC177" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD177" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE177" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF177" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>85</v>
@@ -27405,7 +27402,7 @@
         <v>214</v>
       </c>
       <c r="AS177" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AT177" t="s" s="2">
         <v>84</v>
@@ -27416,10 +27413,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -27445,16 +27442,16 @@
         <v>249</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="M178" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N178" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="N178" t="s" s="2">
+      <c r="O178" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>84</v>
@@ -27464,7 +27461,7 @@
         <v>84</v>
       </c>
       <c r="S178" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="T178" t="s" s="2">
         <v>84</v>
@@ -27482,28 +27479,28 @@
         <v>173</v>
       </c>
       <c r="Y178" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="Z178" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="Z178" t="s" s="2">
+      <c r="AA178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE178" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF178" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="AA178" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB178" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC178" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD178" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE178" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF178" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>85</v>
@@ -27539,10 +27536,10 @@
         <v>84</v>
       </c>
       <c r="AR178" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AS178" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AT178" t="s" s="2">
         <v>84</v>
@@ -27553,10 +27550,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -27582,16 +27579,16 @@
         <v>149</v>
       </c>
       <c r="L179" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M179" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="M179" t="s" s="2">
+      <c r="N179" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="N179" t="s" s="2">
+      <c r="O179" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>84</v>
@@ -27601,46 +27598,46 @@
         <v>84</v>
       </c>
       <c r="S179" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="T179" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="U179" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V179" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W179" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X179" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y179" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z179" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA179" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB179" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC179" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD179" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE179" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF179" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="U179" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V179" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W179" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X179" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y179" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z179" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA179" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB179" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC179" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD179" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE179" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF179" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>85</v>
@@ -27676,13 +27673,13 @@
         <v>84</v>
       </c>
       <c r="AR179" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AS179" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AS179" t="s" s="2">
+      <c r="AT179" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AT179" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="AU179" t="s" s="2">
         <v>84</v>
@@ -27690,10 +27687,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -27719,13 +27716,13 @@
         <v>116</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="M180" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N180" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
@@ -27739,43 +27736,43 @@
         <v>84</v>
       </c>
       <c r="T180" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="U180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE180" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF180" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="U180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE180" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF180" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>85</v>
@@ -27811,13 +27808,13 @@
         <v>84</v>
       </c>
       <c r="AR180" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AS180" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="AS180" t="s" s="2">
+      <c r="AT180" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AT180" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="AU180" t="s" s="2">
         <v>84</v>
@@ -27825,10 +27822,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -27854,10 +27851,10 @@
         <v>269</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M181" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="M181" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -27908,7 +27905,7 @@
         <v>84</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>85</v>
@@ -27944,13 +27941,13 @@
         <v>84</v>
       </c>
       <c r="AR181" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AS181" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="AS181" t="s" s="2">
+      <c r="AT181" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="AT181" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="AU181" t="s" s="2">
         <v>84</v>
@@ -27958,10 +27955,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -27984,16 +27981,16 @@
         <v>103</v>
       </c>
       <c r="K182" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L182" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L182" t="s" s="2">
+      <c r="M182" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M182" t="s" s="2">
+      <c r="N182" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
@@ -28043,7 +28040,7 @@
         <v>84</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>85</v>
@@ -28079,13 +28076,13 @@
         <v>84</v>
       </c>
       <c r="AR182" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AS182" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AS182" t="s" s="2">
+      <c r="AT182" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="AT182" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="AU182" t="s" s="2">
         <v>84</v>
@@ -28093,13 +28090,13 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C183" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="B183" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="C183" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="D183" t="s" s="2">
         <v>84</v>
@@ -28121,17 +28118,17 @@
         <v>103</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>84</v>
@@ -28180,7 +28177,7 @@
         <v>84</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>85</v>
@@ -28216,24 +28213,24 @@
         <v>84</v>
       </c>
       <c r="AR183" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AS183" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AS183" t="s" s="2">
+      <c r="AT183" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="AT183" t="s" s="2">
+      <c r="AU183" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="AU183" t="s" s="2">
-        <v>496</v>
       </c>
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -28363,10 +28360,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -28498,10 +28495,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -28527,16 +28524,16 @@
         <v>191</v>
       </c>
       <c r="L186" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M186" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M186" t="s" s="2">
+      <c r="N186" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N186" t="s" s="2">
+      <c r="O186" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="O186" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>84</v>
@@ -28564,28 +28561,28 @@
         <v>252</v>
       </c>
       <c r="Y186" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="Z186" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="Z186" t="s" s="2">
+      <c r="AA186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF186" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AA186" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB186" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC186" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD186" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE186" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF186" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>85</v>
@@ -28624,7 +28621,7 @@
         <v>214</v>
       </c>
       <c r="AS186" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AT186" t="s" s="2">
         <v>84</v>
@@ -28635,10 +28632,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -28664,16 +28661,16 @@
         <v>249</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="M187" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N187" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="N187" t="s" s="2">
+      <c r="O187" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>84</v>
@@ -28683,7 +28680,7 @@
         <v>84</v>
       </c>
       <c r="S187" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="T187" t="s" s="2">
         <v>84</v>
@@ -28701,28 +28698,28 @@
         <v>173</v>
       </c>
       <c r="Y187" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="Z187" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="Z187" t="s" s="2">
+      <c r="AA187" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB187" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC187" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD187" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE187" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF187" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="AA187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE187" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF187" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>85</v>
@@ -28758,10 +28755,10 @@
         <v>84</v>
       </c>
       <c r="AR187" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AS187" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AT187" t="s" s="2">
         <v>84</v>
@@ -28772,10 +28769,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -28801,16 +28798,16 @@
         <v>149</v>
       </c>
       <c r="L188" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M188" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="M188" t="s" s="2">
+      <c r="N188" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="N188" t="s" s="2">
+      <c r="O188" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>84</v>
@@ -28820,46 +28817,46 @@
         <v>84</v>
       </c>
       <c r="S188" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="T188" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="U188" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V188" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W188" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X188" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y188" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z188" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA188" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB188" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC188" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD188" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE188" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF188" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="U188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE188" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF188" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>85</v>
@@ -28895,13 +28892,13 @@
         <v>84</v>
       </c>
       <c r="AR188" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AS188" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AS188" t="s" s="2">
+      <c r="AT188" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AT188" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="AU188" t="s" s="2">
         <v>84</v>
@@ -28909,10 +28906,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -28938,13 +28935,13 @@
         <v>116</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="M189" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N189" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
@@ -28958,43 +28955,43 @@
         <v>84</v>
       </c>
       <c r="T189" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="U189" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V189" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W189" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X189" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y189" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z189" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA189" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB189" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC189" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD189" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE189" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF189" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="U189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE189" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF189" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>85</v>
@@ -29030,13 +29027,13 @@
         <v>84</v>
       </c>
       <c r="AR189" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AS189" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="AS189" t="s" s="2">
+      <c r="AT189" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AT189" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="AU189" t="s" s="2">
         <v>84</v>
@@ -29044,10 +29041,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -29073,10 +29070,10 @@
         <v>269</v>
       </c>
       <c r="L190" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M190" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="M190" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
@@ -29127,7 +29124,7 @@
         <v>84</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>85</v>
@@ -29163,13 +29160,13 @@
         <v>84</v>
       </c>
       <c r="AR190" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AS190" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="AS190" t="s" s="2">
+      <c r="AT190" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="AT190" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="AU190" t="s" s="2">
         <v>84</v>
@@ -29177,10 +29174,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -29203,16 +29200,16 @@
         <v>103</v>
       </c>
       <c r="K191" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L191" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L191" t="s" s="2">
+      <c r="M191" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M191" t="s" s="2">
+      <c r="N191" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
@@ -29262,7 +29259,7 @@
         <v>84</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>85</v>
@@ -29298,13 +29295,13 @@
         <v>84</v>
       </c>
       <c r="AR191" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AS191" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AS191" t="s" s="2">
+      <c r="AT191" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="AT191" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="AU191" t="s" s="2">
         <v>84</v>
@@ -29312,10 +29309,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -29341,23 +29338,23 @@
         <v>317</v>
       </c>
       <c r="L192" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M192" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="M192" t="s" s="2">
+      <c r="N192" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="N192" t="s" s="2">
+      <c r="O192" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="O192" t="s" s="2">
+      <c r="P192" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q192" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="P192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q192" t="s" s="2">
-        <v>600</v>
-      </c>
       <c r="R192" t="s" s="2">
         <v>84</v>
       </c>
@@ -29401,7 +29398,7 @@
         <v>84</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>85</v>
@@ -29440,21 +29437,21 @@
         <v>84</v>
       </c>
       <c r="AS192" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AT192" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AU192" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AT192" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AU192" t="s" s="2">
-        <v>602</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -29477,19 +29474,19 @@
         <v>84</v>
       </c>
       <c r="K193" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="L193" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="L193" t="s" s="2">
+      <c r="M193" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="M193" t="s" s="2">
+      <c r="N193" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="N193" t="s" s="2">
+      <c r="O193" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="O193" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>84</v>
@@ -29538,7 +29535,7 @@
         <v>84</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>85</v>
@@ -29574,13 +29571,13 @@
         <v>84</v>
       </c>
       <c r="AR193" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AS193" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="AS193" t="s" s="2">
+      <c r="AT193" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="AT193" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="AU193" t="s" s="2">
         <v>84</v>
@@ -29588,10 +29585,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -29721,10 +29718,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -29856,13 +29853,13 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="C196" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="C196" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="D196" t="s" s="2">
         <v>84</v>
@@ -29884,13 +29881,13 @@
         <v>84</v>
       </c>
       <c r="K196" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="L196" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="L196" t="s" s="2">
+      <c r="M196" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="M196" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -29991,10 +29988,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -30020,16 +30017,16 @@
         <v>191</v>
       </c>
       <c r="L197" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M197" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="M197" t="s" s="2">
+      <c r="N197" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="N197" t="s" s="2">
+      <c r="O197" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="O197" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>84</v>
@@ -30058,25 +30055,25 @@
       </c>
       <c r="Y197" s="2"/>
       <c r="Z197" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AA197" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB197" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC197" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD197" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE197" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF197" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="AA197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF197" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>85</v>
@@ -30112,13 +30109,13 @@
         <v>84</v>
       </c>
       <c r="AR197" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AS197" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="AS197" t="s" s="2">
+      <c r="AT197" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="AT197" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="AU197" t="s" s="2">
         <v>84</v>
@@ -30126,10 +30123,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -30155,16 +30152,16 @@
         <v>116</v>
       </c>
       <c r="L198" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M198" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="M198" t="s" s="2">
+      <c r="N198" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="N198" t="s" s="2">
+      <c r="O198" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="O198" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>84</v>
@@ -30213,7 +30210,7 @@
         <v>84</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>85</v>
@@ -30249,10 +30246,10 @@
         <v>84</v>
       </c>
       <c r="AR198" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AS198" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="AS198" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="AT198" t="s" s="2">
         <v>84</v>
@@ -30263,14 +30260,14 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E199" s="2"/>
       <c r="F199" t="s" s="2">
@@ -30292,13 +30289,13 @@
         <v>116</v>
       </c>
       <c r="L199" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M199" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="M199" t="s" s="2">
+      <c r="N199" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="N199" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
@@ -30348,7 +30345,7 @@
         <v>84</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>85</v>
@@ -30366,31 +30363,31 @@
         <v>84</v>
       </c>
       <c r="AL199" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AM199" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN199" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO199" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP199" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ199" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR199" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="AM199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ199" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR199" t="s" s="2">
+      <c r="AS199" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="AS199" t="s" s="2">
+      <c r="AT199" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="AT199" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="AU199" t="s" s="2">
         <v>84</v>
@@ -30398,14 +30395,14 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" t="s" s="2">
@@ -30427,13 +30424,13 @@
         <v>116</v>
       </c>
       <c r="L200" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="M200" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="M200" t="s" s="2">
+      <c r="N200" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -30483,7 +30480,7 @@
         <v>84</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>85</v>
@@ -30501,31 +30498,31 @@
         <v>84</v>
       </c>
       <c r="AL200" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AM200" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN200" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO200" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP200" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ200" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR200" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="AM200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ200" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR200" t="s" s="2">
+      <c r="AS200" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="AS200" t="s" s="2">
+      <c r="AT200" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="AT200" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="AU200" t="s" s="2">
         <v>84</v>
@@ -30533,10 +30530,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -30562,10 +30559,10 @@
         <v>116</v>
       </c>
       <c r="L201" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="M201" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="M201" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
@@ -30595,28 +30592,28 @@
         <v>173</v>
       </c>
       <c r="Y201" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="Z201" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="Z201" t="s" s="2">
+      <c r="AA201" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB201" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC201" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD201" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE201" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF201" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="AA201" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB201" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC201" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD201" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE201" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF201" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>85</v>
@@ -30652,13 +30649,13 @@
         <v>84</v>
       </c>
       <c r="AR201" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AS201" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="AS201" t="s" s="2">
+      <c r="AT201" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="AT201" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="AU201" t="s" s="2">
         <v>84</v>
@@ -30666,10 +30663,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -30695,10 +30692,10 @@
         <v>116</v>
       </c>
       <c r="L202" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="M202" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="M202" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -30728,28 +30725,28 @@
         <v>173</v>
       </c>
       <c r="Y202" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="Z202" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="Z202" t="s" s="2">
+      <c r="AA202" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB202" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC202" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD202" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE202" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF202" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="AA202" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB202" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC202" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD202" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE202" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF202" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>85</v>
@@ -30767,28 +30764,28 @@
         <v>84</v>
       </c>
       <c r="AL202" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AM202" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN202" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO202" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP202" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ202" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR202" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="AM202" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN202" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO202" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP202" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ202" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR202" t="s" s="2">
+      <c r="AS202" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="AS202" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="AT202" t="s" s="2">
         <v>84</v>
@@ -30799,10 +30796,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -30828,14 +30825,14 @@
         <v>269</v>
       </c>
       <c r="L203" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="M203" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="M203" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>84</v>
@@ -30884,7 +30881,7 @@
         <v>84</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>85</v>
@@ -30920,13 +30917,13 @@
         <v>84</v>
       </c>
       <c r="AR203" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AS203" t="s" s="2">
         <v>680</v>
       </c>
-      <c r="AS203" t="s" s="2">
-        <v>681</v>
-      </c>
       <c r="AT203" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AU203" t="s" s="2">
         <v>84</v>
@@ -30934,10 +30931,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -30960,19 +30957,19 @@
         <v>84</v>
       </c>
       <c r="K204" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="L204" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="L204" t="s" s="2">
+      <c r="M204" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="M204" t="s" s="2">
+      <c r="N204" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="N204" t="s" s="2">
+      <c r="O204" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="O204" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>84</v>
@@ -31009,7 +31006,7 @@
         <v>84</v>
       </c>
       <c r="AB204" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="AC204" s="2"/>
       <c r="AD204" t="s" s="2">
@@ -31019,7 +31016,7 @@
         <v>129</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>85</v>
@@ -31031,37 +31028,37 @@
         <v>224</v>
       </c>
       <c r="AJ204" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AK204" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL204" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM204" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN204" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO204" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="AK204" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL204" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM204" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN204" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO204" t="s" s="2">
+      <c r="AP204" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ204" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR204" t="s" s="2">
         <v>690</v>
       </c>
-      <c r="AP204" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ204" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR204" t="s" s="2">
+      <c r="AS204" t="s" s="2">
         <v>691</v>
       </c>
-      <c r="AS204" t="s" s="2">
+      <c r="AT204" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="AT204" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="AU204" t="s" s="2">
         <v>84</v>
@@ -31069,10 +31066,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -31202,10 +31199,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -31337,13 +31334,13 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="C207" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="B207" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="C207" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="D207" t="s" s="2">
         <v>84</v>
@@ -31365,13 +31362,13 @@
         <v>84</v>
       </c>
       <c r="K207" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="L207" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="L207" t="s" s="2">
+      <c r="M207" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="M207" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
@@ -31472,10 +31469,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -31501,10 +31498,10 @@
         <v>191</v>
       </c>
       <c r="L208" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M208" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="M208" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
@@ -31534,37 +31531,37 @@
         <v>252</v>
       </c>
       <c r="Y208" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="Z208" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="Z208" t="s" s="2">
+      <c r="AA208" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB208" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC208" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD208" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE208" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF208" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="AA208" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB208" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC208" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD208" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE208" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF208" t="s" s="2">
+      <c r="AG208" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH208" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI208" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="AG208" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH208" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI208" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="AJ208" t="s" s="2">
         <v>114</v>
@@ -31591,13 +31588,13 @@
         <v>84</v>
       </c>
       <c r="AR208" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AS208" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="AS208" t="s" s="2">
+      <c r="AT208" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="AT208" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="AU208" t="s" s="2">
         <v>84</v>
@@ -31605,10 +31602,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -31634,16 +31631,16 @@
         <v>116</v>
       </c>
       <c r="L209" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="M209" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="M209" t="s" s="2">
+      <c r="N209" t="s" s="2">
         <v>713</v>
       </c>
-      <c r="N209" t="s" s="2">
+      <c r="O209" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="O209" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>84</v>
@@ -31692,7 +31689,7 @@
         <v>84</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>85</v>
@@ -31728,13 +31725,13 @@
         <v>84</v>
       </c>
       <c r="AR209" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AS209" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="AS209" t="s" s="2">
-        <v>718</v>
-      </c>
       <c r="AT209" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AU209" t="s" s="2">
         <v>84</v>
@@ -31742,10 +31739,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -31771,16 +31768,16 @@
         <v>191</v>
       </c>
       <c r="L210" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M210" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="M210" t="s" s="2">
+      <c r="N210" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="N210" t="s" s="2">
+      <c r="O210" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="O210" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>84</v>
@@ -31808,28 +31805,28 @@
         <v>252</v>
       </c>
       <c r="Y210" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="Z210" t="s" s="2">
         <v>724</v>
       </c>
-      <c r="Z210" t="s" s="2">
+      <c r="AA210" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB210" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC210" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD210" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE210" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF210" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="AA210" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB210" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC210" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD210" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE210" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF210" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>85</v>
@@ -31865,13 +31862,13 @@
         <v>84</v>
       </c>
       <c r="AR210" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="AS210" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AT210" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="AS210" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AT210" t="s" s="2">
-        <v>728</v>
       </c>
       <c r="AU210" t="s" s="2">
         <v>84</v>
@@ -31879,10 +31876,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -31905,16 +31902,16 @@
         <v>103</v>
       </c>
       <c r="K211" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="L211" t="s" s="2">
         <v>730</v>
       </c>
-      <c r="L211" t="s" s="2">
+      <c r="M211" t="s" s="2">
         <v>731</v>
       </c>
-      <c r="M211" t="s" s="2">
+      <c r="N211" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="N211" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
@@ -31964,7 +31961,7 @@
         <v>84</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>85</v>
@@ -32014,10 +32011,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -32043,10 +32040,10 @@
         <v>269</v>
       </c>
       <c r="L212" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="M212" t="s" s="2">
         <v>736</v>
-      </c>
-      <c r="M212" t="s" s="2">
-        <v>737</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -32097,7 +32094,7 @@
         <v>84</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>85</v>
@@ -32136,10 +32133,10 @@
         <v>214</v>
       </c>
       <c r="AS212" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AT212" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AU212" t="s" s="2">
         <v>84</v>
@@ -32147,13 +32144,13 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="C213" t="s" s="2">
         <v>739</v>
-      </c>
-      <c r="B213" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="C213" t="s" s="2">
-        <v>740</v>
       </c>
       <c r="D213" t="s" s="2">
         <v>84</v>
@@ -32175,19 +32172,19 @@
         <v>84</v>
       </c>
       <c r="K213" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="L213" t="s" s="2">
         <v>741</v>
       </c>
-      <c r="L213" t="s" s="2">
-        <v>742</v>
-      </c>
       <c r="M213" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="N213" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="N213" t="s" s="2">
+      <c r="O213" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="O213" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>84</v>
@@ -32236,7 +32233,7 @@
         <v>84</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>85</v>
@@ -32248,13 +32245,13 @@
         <v>224</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AK213" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL213" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AM213" t="s" s="2">
         <v>84</v>
@@ -32272,13 +32269,13 @@
         <v>84</v>
       </c>
       <c r="AR213" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AS213" t="s" s="2">
         <v>691</v>
       </c>
-      <c r="AS213" t="s" s="2">
+      <c r="AT213" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="AT213" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="AU213" t="s" s="2">
         <v>84</v>
@@ -32286,10 +32283,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -32419,10 +32416,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -32552,13 +32549,13 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D216" t="s" s="2">
         <v>84</v>
@@ -32580,13 +32577,13 @@
         <v>84</v>
       </c>
       <c r="K216" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="L216" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="L216" t="s" s="2">
+      <c r="M216" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="M216" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -32687,10 +32684,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="B217" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="B217" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -32820,10 +32817,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="B218" t="s" s="2">
         <v>749</v>
-      </c>
-      <c r="B218" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -32953,10 +32950,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="B219" t="s" s="2">
         <v>751</v>
-      </c>
-      <c r="B219" t="s" s="2">
-        <v>752</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -32996,7 +32993,7 @@
       </c>
       <c r="Q219" s="2"/>
       <c r="R219" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="S219" t="s" s="2">
         <v>84</v>
@@ -33088,10 +33085,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="B220" t="s" s="2">
         <v>754</v>
-      </c>
-      <c r="B220" t="s" s="2">
-        <v>755</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -33132,7 +33129,7 @@
         <v>84</v>
       </c>
       <c r="S220" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="T220" t="s" s="2">
         <v>84</v>
@@ -33151,7 +33148,7 @@
       </c>
       <c r="Y220" s="2"/>
       <c r="Z220" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AA220" t="s" s="2">
         <v>84</v>
@@ -33219,13 +33216,13 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="C221" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="B221" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="C221" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="D221" t="s" s="2">
         <v>84</v>
@@ -33247,13 +33244,13 @@
         <v>84</v>
       </c>
       <c r="K221" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="L221" t="s" s="2">
         <v>760</v>
       </c>
-      <c r="L221" t="s" s="2">
+      <c r="M221" t="s" s="2">
         <v>761</v>
-      </c>
-      <c r="M221" t="s" s="2">
-        <v>762</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" s="2"/>
@@ -33354,10 +33351,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -33487,10 +33484,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -33622,10 +33619,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C224" t="s" s="2">
         <v>332</v>
@@ -33653,7 +33650,7 @@
         <v>123</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="M224" t="s" s="2">
         <v>217</v>
@@ -33757,10 +33754,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="B225" t="s" s="2">
         <v>767</v>
-      </c>
-      <c r="B225" t="s" s="2">
-        <v>768</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -33890,10 +33887,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="B226" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="B226" t="s" s="2">
-        <v>770</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -34023,10 +34020,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="B227" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="B227" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -34158,10 +34155,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="B228" t="s" s="2">
         <v>773</v>
-      </c>
-      <c r="B228" t="s" s="2">
-        <v>774</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -34221,7 +34218,7 @@
       </c>
       <c r="Y228" s="2"/>
       <c r="Z228" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AA228" t="s" s="2">
         <v>84</v>
@@ -34289,13 +34286,13 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="C229" t="s" s="2">
         <v>776</v>
-      </c>
-      <c r="B229" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="C229" t="s" s="2">
-        <v>777</v>
       </c>
       <c r="D229" t="s" s="2">
         <v>84</v>
@@ -34424,10 +34421,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -34557,10 +34554,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -34690,10 +34687,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -34733,7 +34730,7 @@
       </c>
       <c r="Q232" s="2"/>
       <c r="R232" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="S232" t="s" s="2">
         <v>84</v>
@@ -34825,10 +34822,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -34958,13 +34955,13 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="C234" t="s" s="2">
         <v>782</v>
-      </c>
-      <c r="B234" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="C234" t="s" s="2">
-        <v>783</v>
       </c>
       <c r="D234" t="s" s="2">
         <v>84</v>
@@ -34989,7 +34986,7 @@
         <v>123</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="M234" t="s" s="2">
         <v>217</v>
@@ -35093,10 +35090,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -35226,10 +35223,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -35359,10 +35356,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -35402,7 +35399,7 @@
       </c>
       <c r="Q237" s="2"/>
       <c r="R237" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="S237" t="s" s="2">
         <v>84</v>
@@ -35494,10 +35491,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -35627,13 +35624,13 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="B239" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="C239" t="s" s="2">
         <v>789</v>
-      </c>
-      <c r="B239" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="C239" t="s" s="2">
-        <v>790</v>
       </c>
       <c r="D239" t="s" s="2">
         <v>84</v>
@@ -35762,10 +35759,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -35895,10 +35892,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -36028,10 +36025,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -36071,7 +36068,7 @@
       </c>
       <c r="Q242" s="2"/>
       <c r="R242" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="S242" t="s" s="2">
         <v>84</v>
@@ -36163,10 +36160,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -36296,13 +36293,13 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="B244" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="C244" t="s" s="2">
         <v>795</v>
-      </c>
-      <c r="B244" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="C244" t="s" s="2">
-        <v>796</v>
       </c>
       <c r="D244" t="s" s="2">
         <v>84</v>
@@ -36327,7 +36324,7 @@
         <v>123</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="M244" t="s" s="2">
         <v>217</v>
@@ -36431,10 +36428,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -36564,10 +36561,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -36697,10 +36694,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -36740,7 +36737,7 @@
       </c>
       <c r="Q247" s="2"/>
       <c r="R247" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="S247" t="s" s="2">
         <v>84</v>
@@ -36832,10 +36829,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -36965,13 +36962,13 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="C249" t="s" s="2">
         <v>802</v>
-      </c>
-      <c r="B249" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="C249" t="s" s="2">
-        <v>803</v>
       </c>
       <c r="D249" t="s" s="2">
         <v>84</v>
@@ -37100,10 +37097,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -37233,10 +37230,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -37366,10 +37363,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -37409,7 +37406,7 @@
       </c>
       <c r="Q252" s="2"/>
       <c r="R252" t="s" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="S252" t="s" s="2">
         <v>84</v>
@@ -37501,10 +37498,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -37634,13 +37631,13 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="B254" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="C254" t="s" s="2">
         <v>808</v>
-      </c>
-      <c r="B254" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="C254" t="s" s="2">
-        <v>809</v>
       </c>
       <c r="D254" t="s" s="2">
         <v>84</v>
@@ -37769,10 +37766,10 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -37902,10 +37899,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -38035,10 +38032,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -38078,7 +38075,7 @@
       </c>
       <c r="Q257" s="2"/>
       <c r="R257" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="S257" t="s" s="2">
         <v>84</v>
@@ -38170,10 +38167,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -38303,10 +38300,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -38346,7 +38343,7 @@
       </c>
       <c r="Q259" s="2"/>
       <c r="R259" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="S259" t="s" s="2">
         <v>84</v>
@@ -38438,10 +38435,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -38571,10 +38568,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -38600,10 +38597,10 @@
         <v>191</v>
       </c>
       <c r="L261" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M261" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="M261" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="N261" s="2"/>
       <c r="O261" s="2"/>
@@ -38615,7 +38612,7 @@
         <v>84</v>
       </c>
       <c r="S261" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="T261" t="s" s="2">
         <v>84</v>
@@ -38633,37 +38630,37 @@
         <v>252</v>
       </c>
       <c r="Y261" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="Z261" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="Z261" t="s" s="2">
+      <c r="AA261" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB261" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC261" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD261" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE261" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF261" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="AA261" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB261" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC261" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD261" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE261" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF261" t="s" s="2">
+      <c r="AG261" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH261" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AI261" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="AG261" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH261" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AI261" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="AJ261" t="s" s="2">
         <v>114</v>
@@ -38690,13 +38687,13 @@
         <v>84</v>
       </c>
       <c r="AR261" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AS261" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="AS261" t="s" s="2">
+      <c r="AT261" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="AT261" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="AU261" t="s" s="2">
         <v>84</v>
@@ -38704,10 +38701,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -38733,16 +38730,16 @@
         <v>116</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="M262" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="N262" t="s" s="2">
         <v>713</v>
       </c>
-      <c r="N262" t="s" s="2">
+      <c r="O262" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="O262" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="P262" t="s" s="2">
         <v>84</v>
@@ -38791,7 +38788,7 @@
         <v>84</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>85</v>
@@ -38827,13 +38824,13 @@
         <v>84</v>
       </c>
       <c r="AR262" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AS262" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="AS262" t="s" s="2">
-        <v>718</v>
-      </c>
       <c r="AT262" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AU262" t="s" s="2">
         <v>84</v>
@@ -38841,10 +38838,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -38870,16 +38867,16 @@
         <v>191</v>
       </c>
       <c r="L263" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M263" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="M263" t="s" s="2">
+      <c r="N263" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="N263" t="s" s="2">
+      <c r="O263" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="O263" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="P263" t="s" s="2">
         <v>84</v>
@@ -38907,28 +38904,28 @@
         <v>252</v>
       </c>
       <c r="Y263" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="Z263" t="s" s="2">
         <v>724</v>
       </c>
-      <c r="Z263" t="s" s="2">
+      <c r="AA263" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB263" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC263" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD263" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE263" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF263" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="AA263" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB263" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC263" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD263" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE263" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF263" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>85</v>
@@ -38964,13 +38961,13 @@
         <v>84</v>
       </c>
       <c r="AR263" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="AS263" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AT263" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="AS263" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AT263" t="s" s="2">
-        <v>728</v>
       </c>
       <c r="AU263" t="s" s="2">
         <v>84</v>
@@ -38978,10 +38975,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -39004,16 +39001,16 @@
         <v>103</v>
       </c>
       <c r="K264" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="L264" t="s" s="2">
         <v>730</v>
       </c>
-      <c r="L264" t="s" s="2">
+      <c r="M264" t="s" s="2">
         <v>731</v>
       </c>
-      <c r="M264" t="s" s="2">
+      <c r="N264" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="N264" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="O264" s="2"/>
       <c r="P264" t="s" s="2">
@@ -39063,7 +39060,7 @@
         <v>84</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>85</v>
@@ -39113,10 +39110,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -39142,10 +39139,10 @@
         <v>269</v>
       </c>
       <c r="L265" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="M265" t="s" s="2">
         <v>736</v>
-      </c>
-      <c r="M265" t="s" s="2">
-        <v>737</v>
       </c>
       <c r="N265" s="2"/>
       <c r="O265" s="2"/>
@@ -39196,7 +39193,7 @@
         <v>84</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>85</v>
@@ -39235,10 +39232,10 @@
         <v>214</v>
       </c>
       <c r="AS265" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AT265" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AU265" t="s" s="2">
         <v>84</v>
@@ -39246,10 +39243,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -39272,19 +39269,19 @@
         <v>84</v>
       </c>
       <c r="K266" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="L266" t="s" s="2">
         <v>825</v>
       </c>
-      <c r="L266" t="s" s="2">
+      <c r="M266" t="s" s="2">
         <v>826</v>
       </c>
-      <c r="M266" t="s" s="2">
+      <c r="N266" t="s" s="2">
         <v>827</v>
       </c>
-      <c r="N266" t="s" s="2">
+      <c r="O266" t="s" s="2">
         <v>828</v>
-      </c>
-      <c r="O266" t="s" s="2">
-        <v>829</v>
       </c>
       <c r="P266" t="s" s="2">
         <v>84</v>
@@ -39333,7 +39330,7 @@
         <v>84</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>85</v>
@@ -39360,22 +39357,22 @@
         <v>84</v>
       </c>
       <c r="AO266" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="AP266" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ266" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR266" t="s" s="2">
         <v>830</v>
       </c>
-      <c r="AP266" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ266" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR266" t="s" s="2">
+      <c r="AS266" t="s" s="2">
         <v>831</v>
       </c>
-      <c r="AS266" t="s" s="2">
+      <c r="AT266" t="s" s="2">
         <v>832</v>
-      </c>
-      <c r="AT266" t="s" s="2">
-        <v>833</v>
       </c>
       <c r="AU266" t="s" s="2">
         <v>84</v>
@@ -39383,10 +39380,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -39412,14 +39409,14 @@
         <v>191</v>
       </c>
       <c r="L267" t="s" s="2">
+        <v>834</v>
+      </c>
+      <c r="M267" t="s" s="2">
         <v>835</v>
-      </c>
-      <c r="M267" t="s" s="2">
-        <v>836</v>
       </c>
       <c r="N267" s="2"/>
       <c r="O267" t="s" s="2">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="P267" t="s" s="2">
         <v>84</v>
@@ -39447,11 +39444,11 @@
         <v>252</v>
       </c>
       <c r="Y267" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="Z267" t="s" s="2">
         <v>838</v>
       </c>
-      <c r="Z267" t="s" s="2">
-        <v>839</v>
-      </c>
       <c r="AA267" t="s" s="2">
         <v>84</v>
       </c>
@@ -39468,7 +39465,7 @@
         <v>84</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>85</v>
@@ -39504,13 +39501,13 @@
         <v>84</v>
       </c>
       <c r="AR267" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="AS267" t="s" s="2">
         <v>840</v>
       </c>
-      <c r="AS267" t="s" s="2">
+      <c r="AT267" t="s" s="2">
         <v>841</v>
-      </c>
-      <c r="AT267" t="s" s="2">
-        <v>842</v>
       </c>
       <c r="AU267" t="s" s="2">
         <v>84</v>
@@ -39518,10 +39515,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -39544,17 +39541,17 @@
         <v>103</v>
       </c>
       <c r="K268" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="L268" t="s" s="2">
         <v>844</v>
       </c>
-      <c r="L268" t="s" s="2">
+      <c r="M268" t="s" s="2">
         <v>845</v>
-      </c>
-      <c r="M268" t="s" s="2">
-        <v>846</v>
       </c>
       <c r="N268" s="2"/>
       <c r="O268" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="P268" t="s" s="2">
         <v>84</v>
@@ -39603,7 +39600,7 @@
         <v>84</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>85</v>
@@ -39639,13 +39636,13 @@
         <v>84</v>
       </c>
       <c r="AR268" t="s" s="2">
+        <v>847</v>
+      </c>
+      <c r="AS268" t="s" s="2">
         <v>848</v>
       </c>
-      <c r="AS268" t="s" s="2">
+      <c r="AT268" t="s" s="2">
         <v>849</v>
-      </c>
-      <c r="AT268" t="s" s="2">
-        <v>850</v>
       </c>
       <c r="AU268" t="s" s="2">
         <v>84</v>
@@ -39653,10 +39650,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -39679,17 +39676,17 @@
         <v>84</v>
       </c>
       <c r="K269" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L269" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="M269" t="s" s="2">
         <v>852</v>
-      </c>
-      <c r="M269" t="s" s="2">
-        <v>853</v>
       </c>
       <c r="N269" s="2"/>
       <c r="O269" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="P269" t="s" s="2">
         <v>84</v>
@@ -39738,7 +39735,7 @@
         <v>84</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>85</v>
@@ -39777,10 +39774,10 @@
         <v>84</v>
       </c>
       <c r="AS269" t="s" s="2">
+        <v>854</v>
+      </c>
+      <c r="AT269" t="s" s="2">
         <v>855</v>
-      </c>
-      <c r="AT269" t="s" s="2">
-        <v>856</v>
       </c>
       <c r="AU269" t="s" s="2">
         <v>84</v>
@@ -39788,10 +39785,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -39814,13 +39811,13 @@
         <v>84</v>
       </c>
       <c r="K270" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="L270" t="s" s="2">
         <v>858</v>
       </c>
-      <c r="L270" t="s" s="2">
+      <c r="M270" t="s" s="2">
         <v>859</v>
-      </c>
-      <c r="M270" t="s" s="2">
-        <v>860</v>
       </c>
       <c r="N270" s="2"/>
       <c r="O270" s="2"/>
@@ -39859,7 +39856,7 @@
         <v>84</v>
       </c>
       <c r="AB270" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="AC270" s="2"/>
       <c r="AD270" t="s" s="2">
@@ -39869,7 +39866,7 @@
         <v>129</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>85</v>
@@ -39905,13 +39902,13 @@
         <v>84</v>
       </c>
       <c r="AR270" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="AS270" t="s" s="2">
         <v>862</v>
       </c>
-      <c r="AS270" t="s" s="2">
+      <c r="AT270" t="s" s="2">
         <v>863</v>
-      </c>
-      <c r="AT270" t="s" s="2">
-        <v>864</v>
       </c>
       <c r="AU270" t="s" s="2">
         <v>84</v>
@@ -39919,10 +39916,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -40052,10 +40049,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -40187,14 +40184,14 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E273" s="2"/>
       <c r="F273" t="s" s="2">
@@ -40216,16 +40213,16 @@
         <v>123</v>
       </c>
       <c r="L273" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="M273" t="s" s="2">
         <v>869</v>
-      </c>
-      <c r="M273" t="s" s="2">
-        <v>870</v>
       </c>
       <c r="N273" t="s" s="2">
         <v>126</v>
       </c>
       <c r="O273" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="P273" t="s" s="2">
         <v>84</v>
@@ -40274,7 +40271,7 @@
         <v>84</v>
       </c>
       <c r="AF273" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AG273" t="s" s="2">
         <v>85</v>
@@ -40324,10 +40321,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -40350,17 +40347,17 @@
         <v>84</v>
       </c>
       <c r="K274" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L274" t="s" s="2">
+        <v>872</v>
+      </c>
+      <c r="M274" t="s" s="2">
         <v>873</v>
-      </c>
-      <c r="M274" t="s" s="2">
-        <v>874</v>
       </c>
       <c r="N274" s="2"/>
       <c r="O274" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="P274" t="s" s="2">
         <v>84</v>
@@ -40409,7 +40406,7 @@
         <v>84</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AG274" t="s" s="2">
         <v>85</v>
@@ -40433,22 +40430,22 @@
         <v>84</v>
       </c>
       <c r="AN274" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="AO274" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP274" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ274" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR274" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS274" t="s" s="2">
         <v>876</v>
-      </c>
-      <c r="AO274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR274" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS274" t="s" s="2">
-        <v>877</v>
       </c>
       <c r="AT274" t="s" s="2">
         <v>84</v>
@@ -40459,10 +40456,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -40488,10 +40485,10 @@
         <v>249</v>
       </c>
       <c r="L275" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="M275" t="s" s="2">
         <v>879</v>
-      </c>
-      <c r="M275" t="s" s="2">
-        <v>880</v>
       </c>
       <c r="N275" s="2"/>
       <c r="O275" s="2"/>
@@ -40521,11 +40518,11 @@
         <v>181</v>
       </c>
       <c r="Y275" t="s" s="2">
+        <v>880</v>
+      </c>
+      <c r="Z275" t="s" s="2">
         <v>881</v>
       </c>
-      <c r="Z275" t="s" s="2">
-        <v>882</v>
-      </c>
       <c r="AA275" t="s" s="2">
         <v>84</v>
       </c>
@@ -40542,7 +40539,7 @@
         <v>84</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>102</v>
@@ -40566,25 +40563,25 @@
         <v>84</v>
       </c>
       <c r="AN275" t="s" s="2">
+        <v>882</v>
+      </c>
+      <c r="AO275" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP275" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ275" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR275" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS275" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="AT275" t="s" s="2">
         <v>883</v>
-      </c>
-      <c r="AO275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR275" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS275" t="s" s="2">
-        <v>863</v>
-      </c>
-      <c r="AT275" t="s" s="2">
-        <v>884</v>
       </c>
       <c r="AU275" t="s" s="2">
         <v>84</v>
@@ -40592,10 +40589,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -40621,14 +40618,14 @@
         <v>269</v>
       </c>
       <c r="L276" t="s" s="2">
+        <v>885</v>
+      </c>
+      <c r="M276" t="s" s="2">
         <v>886</v>
-      </c>
-      <c r="M276" t="s" s="2">
-        <v>887</v>
       </c>
       <c r="N276" s="2"/>
       <c r="O276" t="s" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="P276" t="s" s="2">
         <v>84</v>
@@ -40677,7 +40674,7 @@
         <v>84</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>85</v>
@@ -40716,10 +40713,10 @@
         <v>84</v>
       </c>
       <c r="AS276" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="AT276" t="s" s="2">
         <v>889</v>
-      </c>
-      <c r="AT276" t="s" s="2">
-        <v>890</v>
       </c>
       <c r="AU276" t="s" s="2">
         <v>84</v>
@@ -40727,10 +40724,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -40753,13 +40750,13 @@
         <v>84</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L277" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="M277" t="s" s="2">
         <v>892</v>
-      </c>
-      <c r="M277" t="s" s="2">
-        <v>893</v>
       </c>
       <c r="N277" s="2"/>
       <c r="O277" s="2"/>
@@ -40810,7 +40807,7 @@
         <v>84</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>85</v>
@@ -40849,7 +40846,7 @@
         <v>84</v>
       </c>
       <c r="AS277" t="s" s="2">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="AT277" t="s" s="2">
         <v>84</v>
@@ -40860,13 +40857,13 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
+        <v>894</v>
+      </c>
+      <c r="B278" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="C278" t="s" s="2">
         <v>895</v>
-      </c>
-      <c r="B278" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="C278" t="s" s="2">
-        <v>896</v>
       </c>
       <c r="D278" t="s" s="2">
         <v>84</v>
@@ -40888,13 +40885,13 @@
         <v>84</v>
       </c>
       <c r="K278" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="L278" t="s" s="2">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="M278" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="N278" s="2"/>
       <c r="O278" s="2"/>
@@ -40945,7 +40942,7 @@
         <v>84</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>85</v>
@@ -40969,7 +40966,7 @@
         <v>84</v>
       </c>
       <c r="AN278" t="s" s="2">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="AO278" t="s" s="2">
         <v>84</v>
@@ -40981,13 +40978,13 @@
         <v>84</v>
       </c>
       <c r="AR278" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="AS278" t="s" s="2">
         <v>862</v>
       </c>
-      <c r="AS278" t="s" s="2">
+      <c r="AT278" t="s" s="2">
         <v>863</v>
-      </c>
-      <c r="AT278" t="s" s="2">
-        <v>864</v>
       </c>
       <c r="AU278" t="s" s="2">
         <v>84</v>
@@ -40995,10 +40992,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -41128,10 +41125,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -41259,13 +41256,13 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
+        <v>900</v>
+      </c>
+      <c r="B281" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="C281" t="s" s="2">
         <v>901</v>
-      </c>
-      <c r="B281" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="C281" t="s" s="2">
-        <v>902</v>
       </c>
       <c r="D281" t="s" s="2">
         <v>84</v>
@@ -41287,13 +41284,13 @@
         <v>84</v>
       </c>
       <c r="K281" t="s" s="2">
+        <v>902</v>
+      </c>
+      <c r="L281" t="s" s="2">
         <v>903</v>
       </c>
-      <c r="L281" t="s" s="2">
+      <c r="M281" t="s" s="2">
         <v>904</v>
-      </c>
-      <c r="M281" t="s" s="2">
-        <v>905</v>
       </c>
       <c r="N281" s="2"/>
       <c r="O281" s="2"/>
@@ -41394,10 +41391,10 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
+        <v>905</v>
+      </c>
+      <c r="B282" t="s" s="2">
         <v>906</v>
-      </c>
-      <c r="B282" t="s" s="2">
-        <v>907</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -41527,10 +41524,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="B283" t="s" s="2">
         <v>908</v>
-      </c>
-      <c r="B283" t="s" s="2">
-        <v>909</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -41662,13 +41659,13 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
+        <v>909</v>
+      </c>
+      <c r="B284" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="C284" t="s" s="2">
         <v>910</v>
-      </c>
-      <c r="B284" t="s" s="2">
-        <v>909</v>
-      </c>
-      <c r="C284" t="s" s="2">
-        <v>911</v>
       </c>
       <c r="D284" t="s" s="2">
         <v>84</v>
@@ -41771,7 +41768,7 @@
         <v>84</v>
       </c>
       <c r="AN284" t="s" s="2">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="AO284" t="s" s="2">
         <v>84</v>
@@ -41797,10 +41794,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="B285" t="s" s="2">
         <v>913</v>
-      </c>
-      <c r="B285" t="s" s="2">
-        <v>914</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -41930,10 +41927,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
+        <v>914</v>
+      </c>
+      <c r="B286" t="s" s="2">
         <v>915</v>
-      </c>
-      <c r="B286" t="s" s="2">
-        <v>916</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -42063,10 +42060,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
+        <v>916</v>
+      </c>
+      <c r="B287" t="s" s="2">
         <v>917</v>
-      </c>
-      <c r="B287" t="s" s="2">
-        <v>918</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -42106,7 +42103,7 @@
       </c>
       <c r="Q287" s="2"/>
       <c r="R287" t="s" s="2">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="S287" t="s" s="2">
         <v>84</v>
@@ -42198,10 +42195,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
+        <v>918</v>
+      </c>
+      <c r="B288" t="s" s="2">
         <v>919</v>
-      </c>
-      <c r="B288" t="s" s="2">
-        <v>920</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -42261,7 +42258,7 @@
       </c>
       <c r="Y288" s="2"/>
       <c r="Z288" t="s" s="2">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA288" t="s" s="2">
         <v>84</v>
@@ -42329,13 +42326,13 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
+        <v>921</v>
+      </c>
+      <c r="B289" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="C289" t="s" s="2">
         <v>922</v>
-      </c>
-      <c r="B289" t="s" s="2">
-        <v>909</v>
-      </c>
-      <c r="C289" t="s" s="2">
-        <v>923</v>
       </c>
       <c r="D289" t="s" s="2">
         <v>84</v>
@@ -42438,7 +42435,7 @@
         <v>84</v>
       </c>
       <c r="AN289" t="s" s="2">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="AO289" t="s" s="2">
         <v>84</v>
@@ -42464,10 +42461,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -42597,10 +42594,10 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
@@ -42730,10 +42727,10 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" t="s" s="2">
@@ -42773,7 +42770,7 @@
       </c>
       <c r="Q292" s="2"/>
       <c r="R292" t="s" s="2">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="S292" t="s" s="2">
         <v>84</v>
@@ -42865,10 +42862,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -42928,7 +42925,7 @@
       </c>
       <c r="Y293" s="2"/>
       <c r="Z293" t="s" s="2">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="AA293" t="s" s="2">
         <v>84</v>
@@ -42996,13 +42993,13 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
+        <v>929</v>
+      </c>
+      <c r="B294" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="C294" t="s" s="2">
         <v>930</v>
-      </c>
-      <c r="B294" t="s" s="2">
-        <v>909</v>
-      </c>
-      <c r="C294" t="s" s="2">
-        <v>931</v>
       </c>
       <c r="D294" t="s" s="2">
         <v>84</v>
@@ -43105,7 +43102,7 @@
         <v>84</v>
       </c>
       <c r="AN294" t="s" s="2">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="AO294" t="s" s="2">
         <v>84</v>
@@ -43131,10 +43128,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -43264,10 +43261,10 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -43397,10 +43394,10 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -43440,7 +43437,7 @@
       </c>
       <c r="Q297" s="2"/>
       <c r="R297" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="S297" t="s" s="2">
         <v>84</v>
@@ -43532,10 +43529,10 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -43595,7 +43592,7 @@
       </c>
       <c r="Y298" s="2"/>
       <c r="Z298" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="AA298" t="s" s="2">
         <v>84</v>
@@ -43663,10 +43660,10 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
+        <v>937</v>
+      </c>
+      <c r="B299" t="s" s="2">
         <v>938</v>
-      </c>
-      <c r="B299" t="s" s="2">
-        <v>939</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -43706,7 +43703,7 @@
       </c>
       <c r="Q299" s="2"/>
       <c r="R299" t="s" s="2">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="S299" t="s" s="2">
         <v>84</v>
@@ -43798,10 +43795,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
+        <v>940</v>
+      </c>
+      <c r="B300" t="s" s="2">
         <v>941</v>
-      </c>
-      <c r="B300" t="s" s="2">
-        <v>942</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -43931,14 +43928,14 @@
     </row>
     <row r="301" hidden="true">
       <c r="A301" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C301" s="2"/>
       <c r="D301" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E301" s="2"/>
       <c r="F301" t="s" s="2">
@@ -43960,16 +43957,16 @@
         <v>123</v>
       </c>
       <c r="L301" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="M301" t="s" s="2">
         <v>869</v>
-      </c>
-      <c r="M301" t="s" s="2">
-        <v>870</v>
       </c>
       <c r="N301" t="s" s="2">
         <v>126</v>
       </c>
       <c r="O301" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="P301" t="s" s="2">
         <v>84</v>
@@ -44018,7 +44015,7 @@
         <v>84</v>
       </c>
       <c r="AF301" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AG301" t="s" s="2">
         <v>85</v>
@@ -44068,10 +44065,10 @@
     </row>
     <row r="302" hidden="true">
       <c r="A302" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C302" s="2"/>
       <c r="D302" t="s" s="2">
@@ -44094,17 +44091,17 @@
         <v>84</v>
       </c>
       <c r="K302" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L302" t="s" s="2">
+        <v>872</v>
+      </c>
+      <c r="M302" t="s" s="2">
         <v>873</v>
-      </c>
-      <c r="M302" t="s" s="2">
-        <v>874</v>
       </c>
       <c r="N302" s="2"/>
       <c r="O302" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="P302" t="s" s="2">
         <v>84</v>
@@ -44153,7 +44150,7 @@
         <v>84</v>
       </c>
       <c r="AF302" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AG302" t="s" s="2">
         <v>85</v>
@@ -44192,7 +44189,7 @@
         <v>84</v>
       </c>
       <c r="AS302" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="AT302" t="s" s="2">
         <v>84</v>
@@ -44203,10 +44200,10 @@
     </row>
     <row r="303" hidden="true">
       <c r="A303" t="s" s="2">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C303" s="2"/>
       <c r="D303" t="s" s="2">
@@ -44232,10 +44229,10 @@
         <v>249</v>
       </c>
       <c r="L303" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="M303" t="s" s="2">
         <v>879</v>
-      </c>
-      <c r="M303" t="s" s="2">
-        <v>880</v>
       </c>
       <c r="N303" s="2"/>
       <c r="O303" s="2"/>
@@ -44265,11 +44262,11 @@
         <v>181</v>
       </c>
       <c r="Y303" t="s" s="2">
+        <v>880</v>
+      </c>
+      <c r="Z303" t="s" s="2">
         <v>881</v>
       </c>
-      <c r="Z303" t="s" s="2">
-        <v>882</v>
-      </c>
       <c r="AA303" t="s" s="2">
         <v>84</v>
       </c>
@@ -44286,7 +44283,7 @@
         <v>84</v>
       </c>
       <c r="AF303" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="AG303" t="s" s="2">
         <v>102</v>
@@ -44325,10 +44322,10 @@
         <v>84</v>
       </c>
       <c r="AS303" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="AT303" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="AU303" t="s" s="2">
         <v>84</v>
@@ -44336,10 +44333,10 @@
     </row>
     <row r="304" hidden="true">
       <c r="A304" t="s" s="2">
+        <v>945</v>
+      </c>
+      <c r="B304" t="s" s="2">
         <v>946</v>
-      </c>
-      <c r="B304" t="s" s="2">
-        <v>947</v>
       </c>
       <c r="C304" s="2"/>
       <c r="D304" t="s" s="2">
@@ -44469,10 +44466,10 @@
     </row>
     <row r="305" hidden="true">
       <c r="A305" t="s" s="2">
+        <v>947</v>
+      </c>
+      <c r="B305" t="s" s="2">
         <v>948</v>
-      </c>
-      <c r="B305" t="s" s="2">
-        <v>949</v>
       </c>
       <c r="C305" s="2"/>
       <c r="D305" t="s" s="2">
@@ -44604,10 +44601,10 @@
     </row>
     <row r="306" hidden="true">
       <c r="A306" t="s" s="2">
+        <v>949</v>
+      </c>
+      <c r="B306" t="s" s="2">
         <v>950</v>
-      </c>
-      <c r="B306" t="s" s="2">
-        <v>951</v>
       </c>
       <c r="C306" s="2"/>
       <c r="D306" t="s" s="2">
@@ -44633,16 +44630,16 @@
         <v>169</v>
       </c>
       <c r="L306" t="s" s="2">
+        <v>951</v>
+      </c>
+      <c r="M306" t="s" s="2">
         <v>952</v>
       </c>
-      <c r="M306" t="s" s="2">
+      <c r="N306" t="s" s="2">
         <v>953</v>
       </c>
-      <c r="N306" t="s" s="2">
+      <c r="O306" t="s" s="2">
         <v>954</v>
-      </c>
-      <c r="O306" t="s" s="2">
-        <v>955</v>
       </c>
       <c r="P306" t="s" s="2">
         <v>84</v>
@@ -44686,10 +44683,10 @@
         <v>84</v>
       </c>
       <c r="AE306" t="s" s="2">
+        <v>955</v>
+      </c>
+      <c r="AF306" t="s" s="2">
         <v>956</v>
-      </c>
-      <c r="AF306" t="s" s="2">
-        <v>957</v>
       </c>
       <c r="AG306" t="s" s="2">
         <v>85</v>
@@ -44725,10 +44722,10 @@
         <v>84</v>
       </c>
       <c r="AR306" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="AS306" t="s" s="2">
         <v>958</v>
-      </c>
-      <c r="AS306" t="s" s="2">
-        <v>959</v>
       </c>
       <c r="AT306" t="s" s="2">
         <v>84</v>
@@ -44739,13 +44736,13 @@
     </row>
     <row r="307" hidden="true">
       <c r="A307" t="s" s="2">
+        <v>959</v>
+      </c>
+      <c r="B307" t="s" s="2">
+        <v>950</v>
+      </c>
+      <c r="C307" t="s" s="2">
         <v>960</v>
-      </c>
-      <c r="B307" t="s" s="2">
-        <v>951</v>
-      </c>
-      <c r="C307" t="s" s="2">
-        <v>961</v>
       </c>
       <c r="D307" t="s" s="2">
         <v>84</v>
@@ -44770,16 +44767,16 @@
         <v>169</v>
       </c>
       <c r="L307" t="s" s="2">
+        <v>951</v>
+      </c>
+      <c r="M307" t="s" s="2">
         <v>952</v>
       </c>
-      <c r="M307" t="s" s="2">
+      <c r="N307" t="s" s="2">
         <v>953</v>
       </c>
-      <c r="N307" t="s" s="2">
+      <c r="O307" t="s" s="2">
         <v>954</v>
-      </c>
-      <c r="O307" t="s" s="2">
-        <v>955</v>
       </c>
       <c r="P307" t="s" s="2">
         <v>84</v>
@@ -44808,7 +44805,7 @@
       </c>
       <c r="Y307" s="2"/>
       <c r="Z307" t="s" s="2">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="AA307" t="s" s="2">
         <v>84</v>
@@ -44826,7 +44823,7 @@
         <v>84</v>
       </c>
       <c r="AF307" t="s" s="2">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AG307" t="s" s="2">
         <v>85</v>
@@ -44862,10 +44859,10 @@
         <v>84</v>
       </c>
       <c r="AR307" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="AS307" t="s" s="2">
         <v>958</v>
-      </c>
-      <c r="AS307" t="s" s="2">
-        <v>959</v>
       </c>
       <c r="AT307" t="s" s="2">
         <v>84</v>
@@ -44876,13 +44873,13 @@
     </row>
     <row r="308" hidden="true">
       <c r="A308" t="s" s="2">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D308" t="s" s="2">
         <v>84</v>
@@ -44907,16 +44904,16 @@
         <v>169</v>
       </c>
       <c r="L308" t="s" s="2">
+        <v>951</v>
+      </c>
+      <c r="M308" t="s" s="2">
         <v>952</v>
       </c>
-      <c r="M308" t="s" s="2">
+      <c r="N308" t="s" s="2">
         <v>953</v>
       </c>
-      <c r="N308" t="s" s="2">
+      <c r="O308" t="s" s="2">
         <v>954</v>
-      </c>
-      <c r="O308" t="s" s="2">
-        <v>955</v>
       </c>
       <c r="P308" t="s" s="2">
         <v>84</v>
@@ -44945,7 +44942,7 @@
       </c>
       <c r="Y308" s="2"/>
       <c r="Z308" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="AA308" t="s" s="2">
         <v>84</v>
@@ -44963,7 +44960,7 @@
         <v>84</v>
       </c>
       <c r="AF308" t="s" s="2">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AG308" t="s" s="2">
         <v>85</v>
@@ -44999,10 +44996,10 @@
         <v>84</v>
       </c>
       <c r="AR308" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="AS308" t="s" s="2">
         <v>958</v>
-      </c>
-      <c r="AS308" t="s" s="2">
-        <v>959</v>
       </c>
       <c r="AT308" t="s" s="2">
         <v>84</v>
@@ -45013,10 +45010,10 @@
     </row>
     <row r="309" hidden="true">
       <c r="A309" t="s" s="2">
+        <v>964</v>
+      </c>
+      <c r="B309" t="s" s="2">
         <v>965</v>
-      </c>
-      <c r="B309" t="s" s="2">
-        <v>966</v>
       </c>
       <c r="C309" s="2"/>
       <c r="D309" t="s" s="2">
@@ -45042,16 +45039,16 @@
         <v>116</v>
       </c>
       <c r="L309" t="s" s="2">
+        <v>966</v>
+      </c>
+      <c r="M309" t="s" s="2">
         <v>967</v>
       </c>
-      <c r="M309" t="s" s="2">
+      <c r="N309" t="s" s="2">
         <v>968</v>
       </c>
-      <c r="N309" t="s" s="2">
+      <c r="O309" t="s" s="2">
         <v>969</v>
-      </c>
-      <c r="O309" t="s" s="2">
-        <v>970</v>
       </c>
       <c r="P309" t="s" s="2">
         <v>84</v>
@@ -45100,7 +45097,7 @@
         <v>84</v>
       </c>
       <c r="AF309" t="s" s="2">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="AG309" t="s" s="2">
         <v>85</v>
@@ -45136,10 +45133,10 @@
         <v>84</v>
       </c>
       <c r="AR309" t="s" s="2">
+        <v>971</v>
+      </c>
+      <c r="AS309" t="s" s="2">
         <v>972</v>
-      </c>
-      <c r="AS309" t="s" s="2">
-        <v>973</v>
       </c>
       <c r="AT309" t="s" s="2">
         <v>84</v>
@@ -45150,10 +45147,10 @@
     </row>
     <row r="310" hidden="true">
       <c r="A310" t="s" s="2">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C310" s="2"/>
       <c r="D310" t="s" s="2">
@@ -45179,14 +45176,14 @@
         <v>269</v>
       </c>
       <c r="L310" t="s" s="2">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="M310" t="s" s="2">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="N310" s="2"/>
       <c r="O310" t="s" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="P310" t="s" s="2">
         <v>84</v>
@@ -45235,7 +45232,7 @@
         <v>84</v>
       </c>
       <c r="AF310" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="AG310" t="s" s="2">
         <v>85</v>
@@ -45274,10 +45271,10 @@
         <v>84</v>
       </c>
       <c r="AS310" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="AT310" t="s" s="2">
         <v>889</v>
-      </c>
-      <c r="AT310" t="s" s="2">
-        <v>890</v>
       </c>
       <c r="AU310" t="s" s="2">
         <v>84</v>
@@ -45285,10 +45282,10 @@
     </row>
     <row r="311" hidden="true">
       <c r="A311" t="s" s="2">
+        <v>975</v>
+      </c>
+      <c r="B311" t="s" s="2">
         <v>976</v>
-      </c>
-      <c r="B311" t="s" s="2">
-        <v>977</v>
       </c>
       <c r="C311" s="2"/>
       <c r="D311" t="s" s="2">
@@ -45418,10 +45415,10 @@
     </row>
     <row r="312" hidden="true">
       <c r="A312" t="s" s="2">
+        <v>977</v>
+      </c>
+      <c r="B312" t="s" s="2">
         <v>978</v>
-      </c>
-      <c r="B312" t="s" s="2">
-        <v>979</v>
       </c>
       <c r="C312" s="2"/>
       <c r="D312" t="s" s="2">
@@ -45553,10 +45550,10 @@
     </row>
     <row r="313" hidden="true">
       <c r="A313" t="s" s="2">
+        <v>979</v>
+      </c>
+      <c r="B313" t="s" s="2">
         <v>980</v>
-      </c>
-      <c r="B313" t="s" s="2">
-        <v>981</v>
       </c>
       <c r="C313" s="2"/>
       <c r="D313" t="s" s="2">
@@ -45582,7 +45579,7 @@
         <v>276</v>
       </c>
       <c r="L313" t="s" s="2">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="M313" t="s" s="2">
         <v>278</v>
@@ -45662,7 +45659,7 @@
         <v>84</v>
       </c>
       <c r="AN313" t="s" s="2">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="AO313" t="s" s="2">
         <v>84</v>
@@ -45688,10 +45685,10 @@
     </row>
     <row r="314" hidden="true">
       <c r="A314" t="s" s="2">
+        <v>983</v>
+      </c>
+      <c r="B314" t="s" s="2">
         <v>984</v>
-      </c>
-      <c r="B314" t="s" s="2">
-        <v>985</v>
       </c>
       <c r="C314" s="2"/>
       <c r="D314" t="s" s="2">
@@ -45717,7 +45714,7 @@
         <v>276</v>
       </c>
       <c r="L314" t="s" s="2">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M314" t="s" s="2">
         <v>288</v>
@@ -45799,7 +45796,7 @@
         <v>84</v>
       </c>
       <c r="AN314" t="s" s="2">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="AO314" t="s" s="2">
         <v>84</v>
@@ -45825,10 +45822,10 @@
     </row>
     <row r="315" hidden="true">
       <c r="A315" t="s" s="2">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C315" s="2"/>
       <c r="D315" t="s" s="2">
@@ -45851,13 +45848,13 @@
         <v>84</v>
       </c>
       <c r="K315" t="s" s="2">
+        <v>988</v>
+      </c>
+      <c r="L315" t="s" s="2">
         <v>989</v>
       </c>
-      <c r="L315" t="s" s="2">
-        <v>990</v>
-      </c>
       <c r="M315" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="N315" s="2"/>
       <c r="O315" s="2"/>
@@ -45908,7 +45905,7 @@
         <v>84</v>
       </c>
       <c r="AF315" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="AG315" t="s" s="2">
         <v>85</v>
@@ -45932,7 +45929,7 @@
         <v>84</v>
       </c>
       <c r="AN315" t="s" s="2">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="AO315" t="s" s="2">
         <v>84</v>
@@ -45947,7 +45944,7 @@
         <v>84</v>
       </c>
       <c r="AS315" t="s" s="2">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="AT315" t="s" s="2">
         <v>84</v>
@@ -45958,13 +45955,13 @@
     </row>
     <row r="316" hidden="true">
       <c r="A316" t="s" s="2">
+        <v>991</v>
+      </c>
+      <c r="B316" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="C316" t="s" s="2">
         <v>992</v>
-      </c>
-      <c r="B316" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="C316" t="s" s="2">
-        <v>993</v>
       </c>
       <c r="D316" t="s" s="2">
         <v>84</v>
@@ -45986,13 +45983,13 @@
         <v>84</v>
       </c>
       <c r="K316" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="L316" t="s" s="2">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="M316" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="N316" s="2"/>
       <c r="O316" s="2"/>
@@ -46043,7 +46040,7 @@
         <v>84</v>
       </c>
       <c r="AF316" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AG316" t="s" s="2">
         <v>85</v>
@@ -46079,13 +46076,13 @@
         <v>84</v>
       </c>
       <c r="AR316" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="AS316" t="s" s="2">
         <v>862</v>
       </c>
-      <c r="AS316" t="s" s="2">
+      <c r="AT316" t="s" s="2">
         <v>863</v>
-      </c>
-      <c r="AT316" t="s" s="2">
-        <v>864</v>
       </c>
       <c r="AU316" t="s" s="2">
         <v>84</v>
@@ -46093,10 +46090,10 @@
     </row>
     <row r="317" hidden="true">
       <c r="A317" t="s" s="2">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C317" s="2"/>
       <c r="D317" t="s" s="2">
@@ -46226,10 +46223,10 @@
     </row>
     <row r="318" hidden="true">
       <c r="A318" t="s" s="2">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C318" s="2"/>
       <c r="D318" t="s" s="2">
@@ -46361,14 +46358,14 @@
     </row>
     <row r="319" hidden="true">
       <c r="A319" t="s" s="2">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C319" s="2"/>
       <c r="D319" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E319" s="2"/>
       <c r="F319" t="s" s="2">
@@ -46390,16 +46387,16 @@
         <v>123</v>
       </c>
       <c r="L319" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="M319" t="s" s="2">
         <v>869</v>
-      </c>
-      <c r="M319" t="s" s="2">
-        <v>870</v>
       </c>
       <c r="N319" t="s" s="2">
         <v>126</v>
       </c>
       <c r="O319" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="P319" t="s" s="2">
         <v>84</v>
@@ -46448,7 +46445,7 @@
         <v>84</v>
       </c>
       <c r="AF319" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AG319" t="s" s="2">
         <v>85</v>
@@ -46498,10 +46495,10 @@
     </row>
     <row r="320" hidden="true">
       <c r="A320" t="s" s="2">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C320" s="2"/>
       <c r="D320" t="s" s="2">
@@ -46524,17 +46521,17 @@
         <v>84</v>
       </c>
       <c r="K320" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L320" t="s" s="2">
+        <v>872</v>
+      </c>
+      <c r="M320" t="s" s="2">
         <v>873</v>
-      </c>
-      <c r="M320" t="s" s="2">
-        <v>874</v>
       </c>
       <c r="N320" s="2"/>
       <c r="O320" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="P320" t="s" s="2">
         <v>84</v>
@@ -46583,7 +46580,7 @@
         <v>84</v>
       </c>
       <c r="AF320" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AG320" t="s" s="2">
         <v>85</v>
@@ -46622,7 +46619,7 @@
         <v>84</v>
       </c>
       <c r="AS320" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="AT320" t="s" s="2">
         <v>84</v>
@@ -46633,10 +46630,10 @@
     </row>
     <row r="321" hidden="true">
       <c r="A321" t="s" s="2">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C321" s="2"/>
       <c r="D321" t="s" s="2">
@@ -46662,10 +46659,10 @@
         <v>249</v>
       </c>
       <c r="L321" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="M321" t="s" s="2">
         <v>879</v>
-      </c>
-      <c r="M321" t="s" s="2">
-        <v>880</v>
       </c>
       <c r="N321" s="2"/>
       <c r="O321" s="2"/>
@@ -46695,11 +46692,11 @@
         <v>181</v>
       </c>
       <c r="Y321" t="s" s="2">
+        <v>880</v>
+      </c>
+      <c r="Z321" t="s" s="2">
         <v>881</v>
       </c>
-      <c r="Z321" t="s" s="2">
-        <v>882</v>
-      </c>
       <c r="AA321" t="s" s="2">
         <v>84</v>
       </c>
@@ -46716,7 +46713,7 @@
         <v>84</v>
       </c>
       <c r="AF321" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="AG321" t="s" s="2">
         <v>102</v>
@@ -46755,10 +46752,10 @@
         <v>84</v>
       </c>
       <c r="AS321" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="AT321" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="AU321" t="s" s="2">
         <v>84</v>
@@ -46766,10 +46763,10 @@
     </row>
     <row r="322" hidden="true">
       <c r="A322" t="s" s="2">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="C322" s="2"/>
       <c r="D322" t="s" s="2">
@@ -46899,10 +46896,10 @@
     </row>
     <row r="323" hidden="true">
       <c r="A323" t="s" s="2">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C323" s="2"/>
       <c r="D323" t="s" s="2">
@@ -47034,10 +47031,10 @@
     </row>
     <row r="324" hidden="true">
       <c r="A324" t="s" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C324" s="2"/>
       <c r="D324" t="s" s="2">
@@ -47063,16 +47060,16 @@
         <v>169</v>
       </c>
       <c r="L324" t="s" s="2">
+        <v>951</v>
+      </c>
+      <c r="M324" t="s" s="2">
         <v>952</v>
       </c>
-      <c r="M324" t="s" s="2">
+      <c r="N324" t="s" s="2">
         <v>953</v>
       </c>
-      <c r="N324" t="s" s="2">
+      <c r="O324" t="s" s="2">
         <v>954</v>
-      </c>
-      <c r="O324" t="s" s="2">
-        <v>955</v>
       </c>
       <c r="P324" t="s" s="2">
         <v>84</v>
@@ -47116,10 +47113,10 @@
         <v>84</v>
       </c>
       <c r="AE324" t="s" s="2">
+        <v>955</v>
+      </c>
+      <c r="AF324" t="s" s="2">
         <v>956</v>
-      </c>
-      <c r="AF324" t="s" s="2">
-        <v>957</v>
       </c>
       <c r="AG324" t="s" s="2">
         <v>85</v>
@@ -47155,10 +47152,10 @@
         <v>84</v>
       </c>
       <c r="AR324" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="AS324" t="s" s="2">
         <v>958</v>
-      </c>
-      <c r="AS324" t="s" s="2">
-        <v>959</v>
       </c>
       <c r="AT324" t="s" s="2">
         <v>84</v>
@@ -47169,13 +47166,13 @@
     </row>
     <row r="325" hidden="true">
       <c r="A325" t="s" s="2">
+        <v>1002</v>
+      </c>
+      <c r="B325" t="s" s="2">
+        <v>950</v>
+      </c>
+      <c r="C325" t="s" s="2">
         <v>1003</v>
-      </c>
-      <c r="B325" t="s" s="2">
-        <v>951</v>
-      </c>
-      <c r="C325" t="s" s="2">
-        <v>1004</v>
       </c>
       <c r="D325" t="s" s="2">
         <v>84</v>
@@ -47200,16 +47197,16 @@
         <v>169</v>
       </c>
       <c r="L325" t="s" s="2">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="M325" t="s" s="2">
+        <v>952</v>
+      </c>
+      <c r="N325" t="s" s="2">
         <v>953</v>
       </c>
-      <c r="N325" t="s" s="2">
+      <c r="O325" t="s" s="2">
         <v>954</v>
-      </c>
-      <c r="O325" t="s" s="2">
-        <v>955</v>
       </c>
       <c r="P325" t="s" s="2">
         <v>84</v>
@@ -47238,7 +47235,7 @@
       </c>
       <c r="Y325" s="2"/>
       <c r="Z325" t="s" s="2">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="AA325" t="s" s="2">
         <v>84</v>
@@ -47256,7 +47253,7 @@
         <v>84</v>
       </c>
       <c r="AF325" t="s" s="2">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AG325" t="s" s="2">
         <v>85</v>
@@ -47274,7 +47271,7 @@
         <v>84</v>
       </c>
       <c r="AL325" t="s" s="2">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="AM325" t="s" s="2">
         <v>84</v>
@@ -47292,10 +47289,10 @@
         <v>84</v>
       </c>
       <c r="AR325" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="AS325" t="s" s="2">
         <v>958</v>
-      </c>
-      <c r="AS325" t="s" s="2">
-        <v>959</v>
       </c>
       <c r="AT325" t="s" s="2">
         <v>84</v>
@@ -47306,10 +47303,10 @@
     </row>
     <row r="326" hidden="true">
       <c r="A326" t="s" s="2">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C326" t="s" s="2">
         <v>361</v>
@@ -47337,16 +47334,16 @@
         <v>169</v>
       </c>
       <c r="L326" t="s" s="2">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="M326" t="s" s="2">
+        <v>952</v>
+      </c>
+      <c r="N326" t="s" s="2">
         <v>953</v>
       </c>
-      <c r="N326" t="s" s="2">
+      <c r="O326" t="s" s="2">
         <v>954</v>
-      </c>
-      <c r="O326" t="s" s="2">
-        <v>955</v>
       </c>
       <c r="P326" t="s" s="2">
         <v>84</v>
@@ -47393,7 +47390,7 @@
         <v>84</v>
       </c>
       <c r="AF326" t="s" s="2">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AG326" t="s" s="2">
         <v>85</v>
@@ -47411,7 +47408,7 @@
         <v>84</v>
       </c>
       <c r="AL326" t="s" s="2">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="AM326" t="s" s="2">
         <v>84</v>
@@ -47429,10 +47426,10 @@
         <v>84</v>
       </c>
       <c r="AR326" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="AS326" t="s" s="2">
         <v>958</v>
-      </c>
-      <c r="AS326" t="s" s="2">
-        <v>959</v>
       </c>
       <c r="AT326" t="s" s="2">
         <v>84</v>
@@ -47443,10 +47440,10 @@
     </row>
     <row r="327" hidden="true">
       <c r="A327" t="s" s="2">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C327" s="2"/>
       <c r="D327" t="s" s="2">
@@ -47472,16 +47469,16 @@
         <v>116</v>
       </c>
       <c r="L327" t="s" s="2">
+        <v>966</v>
+      </c>
+      <c r="M327" t="s" s="2">
         <v>967</v>
       </c>
-      <c r="M327" t="s" s="2">
+      <c r="N327" t="s" s="2">
         <v>968</v>
       </c>
-      <c r="N327" t="s" s="2">
+      <c r="O327" t="s" s="2">
         <v>969</v>
-      </c>
-      <c r="O327" t="s" s="2">
-        <v>970</v>
       </c>
       <c r="P327" t="s" s="2">
         <v>84</v>
@@ -47530,7 +47527,7 @@
         <v>84</v>
       </c>
       <c r="AF327" t="s" s="2">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="AG327" t="s" s="2">
         <v>85</v>
@@ -47566,10 +47563,10 @@
         <v>84</v>
       </c>
       <c r="AR327" t="s" s="2">
+        <v>971</v>
+      </c>
+      <c r="AS327" t="s" s="2">
         <v>972</v>
-      </c>
-      <c r="AS327" t="s" s="2">
-        <v>973</v>
       </c>
       <c r="AT327" t="s" s="2">
         <v>84</v>
@@ -47580,10 +47577,10 @@
     </row>
     <row r="328" hidden="true">
       <c r="A328" t="s" s="2">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C328" s="2"/>
       <c r="D328" t="s" s="2">
@@ -47609,14 +47606,14 @@
         <v>269</v>
       </c>
       <c r="L328" t="s" s="2">
+        <v>885</v>
+      </c>
+      <c r="M328" t="s" s="2">
         <v>886</v>
-      </c>
-      <c r="M328" t="s" s="2">
-        <v>887</v>
       </c>
       <c r="N328" s="2"/>
       <c r="O328" t="s" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="P328" t="s" s="2">
         <v>84</v>
@@ -47665,7 +47662,7 @@
         <v>84</v>
       </c>
       <c r="AF328" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="AG328" t="s" s="2">
         <v>85</v>
@@ -47704,10 +47701,10 @@
         <v>84</v>
       </c>
       <c r="AS328" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="AT328" t="s" s="2">
         <v>889</v>
-      </c>
-      <c r="AT328" t="s" s="2">
-        <v>890</v>
       </c>
       <c r="AU328" t="s" s="2">
         <v>84</v>
@@ -47715,10 +47712,10 @@
     </row>
     <row r="329" hidden="true">
       <c r="A329" t="s" s="2">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C329" s="2"/>
       <c r="D329" t="s" s="2">
@@ -47848,10 +47845,10 @@
     </row>
     <row r="330" hidden="true">
       <c r="A330" t="s" s="2">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C330" s="2"/>
       <c r="D330" t="s" s="2">
@@ -47983,10 +47980,10 @@
     </row>
     <row r="331" hidden="true">
       <c r="A331" t="s" s="2">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C331" s="2"/>
       <c r="D331" t="s" s="2">
@@ -48012,7 +48009,7 @@
         <v>276</v>
       </c>
       <c r="L331" t="s" s="2">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="M331" t="s" s="2">
         <v>278</v>
@@ -48086,7 +48083,7 @@
         <v>84</v>
       </c>
       <c r="AL331" t="s" s="2">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="AM331" t="s" s="2">
         <v>84</v>
@@ -48118,10 +48115,10 @@
     </row>
     <row r="332" hidden="true">
       <c r="A332" t="s" s="2">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C332" s="2"/>
       <c r="D332" t="s" s="2">
@@ -48147,7 +48144,7 @@
         <v>276</v>
       </c>
       <c r="L332" t="s" s="2">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="M332" t="s" s="2">
         <v>288</v>
@@ -48223,7 +48220,7 @@
         <v>84</v>
       </c>
       <c r="AL332" t="s" s="2">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="AM332" t="s" s="2">
         <v>84</v>
@@ -48255,10 +48252,10 @@
     </row>
     <row r="333" hidden="true">
       <c r="A333" t="s" s="2">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C333" s="2"/>
       <c r="D333" t="s" s="2">
@@ -48281,13 +48278,13 @@
         <v>84</v>
       </c>
       <c r="K333" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L333" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="M333" t="s" s="2">
         <v>892</v>
-      </c>
-      <c r="M333" t="s" s="2">
-        <v>893</v>
       </c>
       <c r="N333" s="2"/>
       <c r="O333" s="2"/>
@@ -48338,7 +48335,7 @@
         <v>84</v>
       </c>
       <c r="AF333" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="AG333" t="s" s="2">
         <v>85</v>
@@ -48377,7 +48374,7 @@
         <v>84</v>
       </c>
       <c r="AS333" t="s" s="2">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="AT333" t="s" s="2">
         <v>84</v>
@@ -48388,13 +48385,13 @@
     </row>
     <row r="334" hidden="true">
       <c r="A334" t="s" s="2">
+        <v>1021</v>
+      </c>
+      <c r="B334" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="C334" t="s" s="2">
         <v>1022</v>
-      </c>
-      <c r="B334" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="C334" t="s" s="2">
-        <v>1023</v>
       </c>
       <c r="D334" t="s" s="2">
         <v>84</v>
@@ -48416,13 +48413,13 @@
         <v>84</v>
       </c>
       <c r="K334" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="L334" t="s" s="2">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="M334" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="N334" s="2"/>
       <c r="O334" s="2"/>
@@ -48473,7 +48470,7 @@
         <v>84</v>
       </c>
       <c r="AF334" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AG334" t="s" s="2">
         <v>85</v>
@@ -48509,13 +48506,13 @@
         <v>84</v>
       </c>
       <c r="AR334" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="AS334" t="s" s="2">
         <v>862</v>
       </c>
-      <c r="AS334" t="s" s="2">
+      <c r="AT334" t="s" s="2">
         <v>863</v>
-      </c>
-      <c r="AT334" t="s" s="2">
-        <v>864</v>
       </c>
       <c r="AU334" t="s" s="2">
         <v>84</v>
@@ -48523,10 +48520,10 @@
     </row>
     <row r="335" hidden="true">
       <c r="A335" t="s" s="2">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C335" s="2"/>
       <c r="D335" t="s" s="2">
@@ -48656,10 +48653,10 @@
     </row>
     <row r="336" hidden="true">
       <c r="A336" t="s" s="2">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C336" s="2"/>
       <c r="D336" t="s" s="2">
@@ -48791,14 +48788,14 @@
     </row>
     <row r="337" hidden="true">
       <c r="A337" t="s" s="2">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C337" s="2"/>
       <c r="D337" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E337" s="2"/>
       <c r="F337" t="s" s="2">
@@ -48820,16 +48817,16 @@
         <v>123</v>
       </c>
       <c r="L337" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="M337" t="s" s="2">
         <v>869</v>
-      </c>
-      <c r="M337" t="s" s="2">
-        <v>870</v>
       </c>
       <c r="N337" t="s" s="2">
         <v>126</v>
       </c>
       <c r="O337" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="P337" t="s" s="2">
         <v>84</v>
@@ -48878,7 +48875,7 @@
         <v>84</v>
       </c>
       <c r="AF337" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AG337" t="s" s="2">
         <v>85</v>
@@ -48928,10 +48925,10 @@
     </row>
     <row r="338" hidden="true">
       <c r="A338" t="s" s="2">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C338" s="2"/>
       <c r="D338" t="s" s="2">
@@ -48954,17 +48951,17 @@
         <v>84</v>
       </c>
       <c r="K338" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L338" t="s" s="2">
+        <v>872</v>
+      </c>
+      <c r="M338" t="s" s="2">
         <v>873</v>
-      </c>
-      <c r="M338" t="s" s="2">
-        <v>874</v>
       </c>
       <c r="N338" s="2"/>
       <c r="O338" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="P338" t="s" s="2">
         <v>84</v>
@@ -49013,7 +49010,7 @@
         <v>84</v>
       </c>
       <c r="AF338" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AG338" t="s" s="2">
         <v>85</v>
@@ -49052,7 +49049,7 @@
         <v>84</v>
       </c>
       <c r="AS338" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="AT338" t="s" s="2">
         <v>84</v>
@@ -49063,10 +49060,10 @@
     </row>
     <row r="339" hidden="true">
       <c r="A339" t="s" s="2">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C339" s="2"/>
       <c r="D339" t="s" s="2">
@@ -49092,10 +49089,10 @@
         <v>249</v>
       </c>
       <c r="L339" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="M339" t="s" s="2">
         <v>879</v>
-      </c>
-      <c r="M339" t="s" s="2">
-        <v>880</v>
       </c>
       <c r="N339" s="2"/>
       <c r="O339" s="2"/>
@@ -49125,11 +49122,11 @@
         <v>181</v>
       </c>
       <c r="Y339" t="s" s="2">
+        <v>880</v>
+      </c>
+      <c r="Z339" t="s" s="2">
         <v>881</v>
       </c>
-      <c r="Z339" t="s" s="2">
-        <v>882</v>
-      </c>
       <c r="AA339" t="s" s="2">
         <v>84</v>
       </c>
@@ -49146,7 +49143,7 @@
         <v>84</v>
       </c>
       <c r="AF339" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="AG339" t="s" s="2">
         <v>102</v>
@@ -49161,7 +49158,7 @@
         <v>114</v>
       </c>
       <c r="AK339" t="s" s="2">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="AL339" t="s" s="2">
         <v>84</v>
@@ -49185,10 +49182,10 @@
         <v>84</v>
       </c>
       <c r="AS339" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="AT339" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="AU339" t="s" s="2">
         <v>84</v>
@@ -49196,10 +49193,10 @@
     </row>
     <row r="340" hidden="true">
       <c r="A340" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="C340" s="2"/>
       <c r="D340" t="s" s="2">
@@ -49329,10 +49326,10 @@
     </row>
     <row r="341" hidden="true">
       <c r="A341" t="s" s="2">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C341" s="2"/>
       <c r="D341" t="s" s="2">
@@ -49464,10 +49461,10 @@
     </row>
     <row r="342" hidden="true">
       <c r="A342" t="s" s="2">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C342" s="2"/>
       <c r="D342" t="s" s="2">
@@ -49493,16 +49490,16 @@
         <v>169</v>
       </c>
       <c r="L342" t="s" s="2">
+        <v>951</v>
+      </c>
+      <c r="M342" t="s" s="2">
         <v>952</v>
       </c>
-      <c r="M342" t="s" s="2">
+      <c r="N342" t="s" s="2">
         <v>953</v>
       </c>
-      <c r="N342" t="s" s="2">
+      <c r="O342" t="s" s="2">
         <v>954</v>
-      </c>
-      <c r="O342" t="s" s="2">
-        <v>955</v>
       </c>
       <c r="P342" t="s" s="2">
         <v>84</v>
@@ -49546,10 +49543,10 @@
         <v>84</v>
       </c>
       <c r="AE342" t="s" s="2">
+        <v>955</v>
+      </c>
+      <c r="AF342" t="s" s="2">
         <v>956</v>
-      </c>
-      <c r="AF342" t="s" s="2">
-        <v>957</v>
       </c>
       <c r="AG342" t="s" s="2">
         <v>85</v>
@@ -49585,10 +49582,10 @@
         <v>84</v>
       </c>
       <c r="AR342" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="AS342" t="s" s="2">
         <v>958</v>
-      </c>
-      <c r="AS342" t="s" s="2">
-        <v>959</v>
       </c>
       <c r="AT342" t="s" s="2">
         <v>84</v>
@@ -49599,13 +49596,13 @@
     </row>
     <row r="343" hidden="true">
       <c r="A343" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="B343" t="s" s="2">
+        <v>950</v>
+      </c>
+      <c r="C343" t="s" s="2">
         <v>1034</v>
-      </c>
-      <c r="B343" t="s" s="2">
-        <v>951</v>
-      </c>
-      <c r="C343" t="s" s="2">
-        <v>1035</v>
       </c>
       <c r="D343" t="s" s="2">
         <v>84</v>
@@ -49630,16 +49627,16 @@
         <v>169</v>
       </c>
       <c r="L343" t="s" s="2">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="M343" t="s" s="2">
+        <v>952</v>
+      </c>
+      <c r="N343" t="s" s="2">
         <v>953</v>
       </c>
-      <c r="N343" t="s" s="2">
+      <c r="O343" t="s" s="2">
         <v>954</v>
-      </c>
-      <c r="O343" t="s" s="2">
-        <v>955</v>
       </c>
       <c r="P343" t="s" s="2">
         <v>84</v>
@@ -49668,7 +49665,7 @@
       </c>
       <c r="Y343" s="2"/>
       <c r="Z343" t="s" s="2">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="AA343" t="s" s="2">
         <v>84</v>
@@ -49686,7 +49683,7 @@
         <v>84</v>
       </c>
       <c r="AF343" t="s" s="2">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AG343" t="s" s="2">
         <v>85</v>
@@ -49701,7 +49698,7 @@
         <v>114</v>
       </c>
       <c r="AK343" t="s" s="2">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="AL343" t="s" s="2">
         <v>84</v>
@@ -49722,10 +49719,10 @@
         <v>84</v>
       </c>
       <c r="AR343" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="AS343" t="s" s="2">
         <v>958</v>
-      </c>
-      <c r="AS343" t="s" s="2">
-        <v>959</v>
       </c>
       <c r="AT343" t="s" s="2">
         <v>84</v>
@@ -49736,13 +49733,13 @@
     </row>
     <row r="344" hidden="true">
       <c r="A344" t="s" s="2">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="D344" t="s" s="2">
         <v>84</v>
@@ -49767,16 +49764,16 @@
         <v>169</v>
       </c>
       <c r="L344" t="s" s="2">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="M344" t="s" s="2">
+        <v>952</v>
+      </c>
+      <c r="N344" t="s" s="2">
         <v>953</v>
       </c>
-      <c r="N344" t="s" s="2">
+      <c r="O344" t="s" s="2">
         <v>954</v>
-      </c>
-      <c r="O344" t="s" s="2">
-        <v>955</v>
       </c>
       <c r="P344" t="s" s="2">
         <v>84</v>
@@ -49805,7 +49802,7 @@
       </c>
       <c r="Y344" s="2"/>
       <c r="Z344" t="s" s="2">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="AA344" t="s" s="2">
         <v>84</v>
@@ -49823,7 +49820,7 @@
         <v>84</v>
       </c>
       <c r="AF344" t="s" s="2">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="AG344" t="s" s="2">
         <v>85</v>
@@ -49859,10 +49856,10 @@
         <v>84</v>
       </c>
       <c r="AR344" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="AS344" t="s" s="2">
         <v>958</v>
-      </c>
-      <c r="AS344" t="s" s="2">
-        <v>959</v>
       </c>
       <c r="AT344" t="s" s="2">
         <v>84</v>
@@ -49873,10 +49870,10 @@
     </row>
     <row r="345" hidden="true">
       <c r="A345" t="s" s="2">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C345" s="2"/>
       <c r="D345" t="s" s="2">
@@ -49902,16 +49899,16 @@
         <v>116</v>
       </c>
       <c r="L345" t="s" s="2">
+        <v>966</v>
+      </c>
+      <c r="M345" t="s" s="2">
         <v>967</v>
       </c>
-      <c r="M345" t="s" s="2">
+      <c r="N345" t="s" s="2">
         <v>968</v>
       </c>
-      <c r="N345" t="s" s="2">
+      <c r="O345" t="s" s="2">
         <v>969</v>
-      </c>
-      <c r="O345" t="s" s="2">
-        <v>970</v>
       </c>
       <c r="P345" t="s" s="2">
         <v>84</v>
@@ -49960,7 +49957,7 @@
         <v>84</v>
       </c>
       <c r="AF345" t="s" s="2">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="AG345" t="s" s="2">
         <v>85</v>
@@ -49996,10 +49993,10 @@
         <v>84</v>
       </c>
       <c r="AR345" t="s" s="2">
+        <v>971</v>
+      </c>
+      <c r="AS345" t="s" s="2">
         <v>972</v>
-      </c>
-      <c r="AS345" t="s" s="2">
-        <v>973</v>
       </c>
       <c r="AT345" t="s" s="2">
         <v>84</v>
@@ -50010,10 +50007,10 @@
     </row>
     <row r="346" hidden="true">
       <c r="A346" t="s" s="2">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C346" s="2"/>
       <c r="D346" t="s" s="2">
@@ -50039,14 +50036,14 @@
         <v>269</v>
       </c>
       <c r="L346" t="s" s="2">
+        <v>885</v>
+      </c>
+      <c r="M346" t="s" s="2">
         <v>886</v>
-      </c>
-      <c r="M346" t="s" s="2">
-        <v>887</v>
       </c>
       <c r="N346" s="2"/>
       <c r="O346" t="s" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="P346" t="s" s="2">
         <v>84</v>
@@ -50095,7 +50092,7 @@
         <v>84</v>
       </c>
       <c r="AF346" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="AG346" t="s" s="2">
         <v>85</v>
@@ -50134,10 +50131,10 @@
         <v>84</v>
       </c>
       <c r="AS346" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="AT346" t="s" s="2">
         <v>889</v>
-      </c>
-      <c r="AT346" t="s" s="2">
-        <v>890</v>
       </c>
       <c r="AU346" t="s" s="2">
         <v>84</v>
@@ -50145,10 +50142,10 @@
     </row>
     <row r="347" hidden="true">
       <c r="A347" t="s" s="2">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C347" s="2"/>
       <c r="D347" t="s" s="2">
@@ -50278,10 +50275,10 @@
     </row>
     <row r="348" hidden="true">
       <c r="A348" t="s" s="2">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C348" s="2"/>
       <c r="D348" t="s" s="2">
@@ -50413,10 +50410,10 @@
     </row>
     <row r="349" hidden="true">
       <c r="A349" t="s" s="2">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C349" s="2"/>
       <c r="D349" t="s" s="2">
@@ -50442,7 +50439,7 @@
         <v>276</v>
       </c>
       <c r="L349" t="s" s="2">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="M349" t="s" s="2">
         <v>278</v>
@@ -50513,7 +50510,7 @@
         <v>114</v>
       </c>
       <c r="AK349" t="s" s="2">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="AL349" t="s" s="2">
         <v>84</v>
@@ -50548,10 +50545,10 @@
     </row>
     <row r="350" hidden="true">
       <c r="A350" t="s" s="2">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C350" s="2"/>
       <c r="D350" t="s" s="2">
@@ -50577,7 +50574,7 @@
         <v>276</v>
       </c>
       <c r="L350" t="s" s="2">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="M350" t="s" s="2">
         <v>288</v>
@@ -50650,7 +50647,7 @@
         <v>114</v>
       </c>
       <c r="AK350" t="s" s="2">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="AL350" t="s" s="2">
         <v>84</v>
@@ -50685,10 +50682,10 @@
     </row>
     <row r="351" hidden="true">
       <c r="A351" t="s" s="2">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C351" s="2"/>
       <c r="D351" t="s" s="2">
@@ -50711,13 +50708,13 @@
         <v>84</v>
       </c>
       <c r="K351" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L351" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="M351" t="s" s="2">
         <v>892</v>
-      </c>
-      <c r="M351" t="s" s="2">
-        <v>893</v>
       </c>
       <c r="N351" s="2"/>
       <c r="O351" s="2"/>
@@ -50768,7 +50765,7 @@
         <v>84</v>
       </c>
       <c r="AF351" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="AG351" t="s" s="2">
         <v>85</v>
@@ -50807,7 +50804,7 @@
         <v>84</v>
       </c>
       <c r="AS351" t="s" s="2">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="AT351" t="s" s="2">
         <v>84</v>
@@ -50818,10 +50815,10 @@
     </row>
     <row r="352" hidden="true">
       <c r="A352" t="s" s="2">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C352" s="2"/>
       <c r="D352" t="s" s="2">
@@ -50844,19 +50841,19 @@
         <v>84</v>
       </c>
       <c r="K352" t="s" s="2">
+        <v>1053</v>
+      </c>
+      <c r="L352" t="s" s="2">
         <v>1054</v>
       </c>
-      <c r="L352" t="s" s="2">
+      <c r="M352" t="s" s="2">
         <v>1055</v>
       </c>
-      <c r="M352" t="s" s="2">
+      <c r="N352" t="s" s="2">
         <v>1056</v>
       </c>
-      <c r="N352" t="s" s="2">
+      <c r="O352" t="s" s="2">
         <v>1057</v>
-      </c>
-      <c r="O352" t="s" s="2">
-        <v>1058</v>
       </c>
       <c r="P352" t="s" s="2">
         <v>84</v>
@@ -50885,7 +50882,7 @@
       </c>
       <c r="Y352" s="2"/>
       <c r="Z352" t="s" s="2">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AA352" t="s" s="2">
         <v>84</v>
@@ -50903,7 +50900,7 @@
         <v>84</v>
       </c>
       <c r="AF352" t="s" s="2">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="AG352" t="s" s="2">
         <v>85</v>
@@ -50939,13 +50936,13 @@
         <v>84</v>
       </c>
       <c r="AR352" t="s" s="2">
+        <v>1059</v>
+      </c>
+      <c r="AS352" t="s" s="2">
         <v>1060</v>
       </c>
-      <c r="AS352" t="s" s="2">
+      <c r="AT352" t="s" s="2">
         <v>1061</v>
-      </c>
-      <c r="AT352" t="s" s="2">
-        <v>1062</v>
       </c>
       <c r="AU352" t="s" s="2">
         <v>84</v>
